--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19750500</v>
+        <v>19494000</v>
       </c>
       <c r="E8" s="3">
-        <v>19171500</v>
+        <v>18922500</v>
       </c>
       <c r="F8" s="3">
-        <v>18415800</v>
+        <v>18176700</v>
       </c>
       <c r="G8" s="3">
-        <v>18743400</v>
+        <v>18500000</v>
       </c>
       <c r="H8" s="3">
-        <v>18064300</v>
+        <v>17829700</v>
       </c>
       <c r="I8" s="3">
-        <v>18008200</v>
+        <v>17774300</v>
       </c>
       <c r="J8" s="3">
-        <v>17512600</v>
+        <v>17285200</v>
       </c>
       <c r="K8" s="3">
         <v>16488100</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7383400</v>
+        <v>7287500</v>
       </c>
       <c r="E9" s="3">
-        <v>7610900</v>
+        <v>7512000</v>
       </c>
       <c r="F9" s="3">
-        <v>7435100</v>
+        <v>7338600</v>
       </c>
       <c r="G9" s="3">
-        <v>7844800</v>
+        <v>7742900</v>
       </c>
       <c r="H9" s="3">
-        <v>7269700</v>
+        <v>7175300</v>
       </c>
       <c r="I9" s="3">
-        <v>7118100</v>
+        <v>7025600</v>
       </c>
       <c r="J9" s="3">
-        <v>6813300</v>
+        <v>6724800</v>
       </c>
       <c r="K9" s="3">
         <v>6518700</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12367100</v>
+        <v>12206500</v>
       </c>
       <c r="E10" s="3">
-        <v>11560600</v>
+        <v>11410500</v>
       </c>
       <c r="F10" s="3">
-        <v>10980700</v>
+        <v>10838100</v>
       </c>
       <c r="G10" s="3">
-        <v>10898600</v>
+        <v>10757000</v>
       </c>
       <c r="H10" s="3">
-        <v>10794600</v>
+        <v>10654400</v>
       </c>
       <c r="I10" s="3">
-        <v>10890100</v>
+        <v>10748700</v>
       </c>
       <c r="J10" s="3">
-        <v>10699400</v>
+        <v>10560400</v>
       </c>
       <c r="K10" s="3">
         <v>9969400</v>
@@ -867,25 +867,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>134700</v>
+        <v>133000</v>
       </c>
       <c r="E12" s="3">
-        <v>130100</v>
+        <v>128400</v>
       </c>
       <c r="F12" s="3">
-        <v>120800</v>
+        <v>119300</v>
       </c>
       <c r="G12" s="3">
-        <v>127100</v>
+        <v>125400</v>
       </c>
       <c r="H12" s="3">
-        <v>136100</v>
+        <v>134300</v>
       </c>
       <c r="I12" s="3">
-        <v>129800</v>
+        <v>128200</v>
       </c>
       <c r="J12" s="3">
-        <v>129300</v>
+        <v>127600</v>
       </c>
       <c r="K12" s="3">
         <v>136000</v>
@@ -951,25 +951,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-282900</v>
+        <v>-279200</v>
       </c>
       <c r="E14" s="3">
-        <v>-99800</v>
+        <v>-98500</v>
       </c>
       <c r="F14" s="3">
-        <v>94900</v>
+        <v>93700</v>
       </c>
       <c r="G14" s="3">
         <v>-3900</v>
       </c>
       <c r="H14" s="3">
-        <v>-58500</v>
+        <v>-57800</v>
       </c>
       <c r="I14" s="3">
-        <v>-5800</v>
+        <v>-5700</v>
       </c>
       <c r="J14" s="3">
-        <v>40800</v>
+        <v>40300</v>
       </c>
       <c r="K14" s="3">
         <v>115900</v>
@@ -993,25 +993,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2815000</v>
+        <v>2778500</v>
       </c>
       <c r="E15" s="3">
-        <v>2777900</v>
+        <v>2741800</v>
       </c>
       <c r="F15" s="3">
-        <v>2798400</v>
+        <v>2762100</v>
       </c>
       <c r="G15" s="3">
-        <v>2794700</v>
+        <v>2758400</v>
       </c>
       <c r="H15" s="3">
-        <v>2526900</v>
+        <v>2494100</v>
       </c>
       <c r="I15" s="3">
-        <v>2590700</v>
+        <v>2557000</v>
       </c>
       <c r="J15" s="3">
-        <v>2575900</v>
+        <v>2542400</v>
       </c>
       <c r="K15" s="3">
         <v>2470600</v>
@@ -1050,25 +1050,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>18166200</v>
+        <v>17930300</v>
       </c>
       <c r="E17" s="3">
-        <v>17784400</v>
+        <v>17553400</v>
       </c>
       <c r="F17" s="3">
-        <v>17599000</v>
+        <v>17370400</v>
       </c>
       <c r="G17" s="3">
-        <v>17846600</v>
+        <v>17614800</v>
       </c>
       <c r="H17" s="3">
-        <v>17034400</v>
+        <v>16813200</v>
       </c>
       <c r="I17" s="3">
-        <v>16943400</v>
+        <v>16723400</v>
       </c>
       <c r="J17" s="3">
-        <v>16444700</v>
+        <v>16231100</v>
       </c>
       <c r="K17" s="3">
         <v>15647200</v>
@@ -1092,25 +1092,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1584300</v>
+        <v>1563700</v>
       </c>
       <c r="E18" s="3">
-        <v>1387100</v>
+        <v>1369100</v>
       </c>
       <c r="F18" s="3">
-        <v>816900</v>
+        <v>806200</v>
       </c>
       <c r="G18" s="3">
-        <v>896800</v>
+        <v>885100</v>
       </c>
       <c r="H18" s="3">
-        <v>1029900</v>
+        <v>1016500</v>
       </c>
       <c r="I18" s="3">
-        <v>1064800</v>
+        <v>1051000</v>
       </c>
       <c r="J18" s="3">
-        <v>1067900</v>
+        <v>1054100</v>
       </c>
       <c r="K18" s="3">
         <v>840900</v>
@@ -1152,25 +1152,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>100400</v>
+        <v>99100</v>
       </c>
       <c r="E20" s="3">
-        <v>339100</v>
+        <v>334700</v>
       </c>
       <c r="F20" s="3">
-        <v>136900</v>
+        <v>135100</v>
       </c>
       <c r="G20" s="3">
-        <v>69300</v>
+        <v>68400</v>
       </c>
       <c r="H20" s="3">
-        <v>38600</v>
+        <v>38100</v>
       </c>
       <c r="I20" s="3">
-        <v>-187400</v>
+        <v>-184900</v>
       </c>
       <c r="J20" s="3">
-        <v>59500</v>
+        <v>58800</v>
       </c>
       <c r="K20" s="3">
         <v>-22900</v>
@@ -1197,22 +1197,22 @@
         <v>24</v>
       </c>
       <c r="E21" s="3">
-        <v>4534600</v>
+        <v>4475800</v>
       </c>
       <c r="F21" s="3">
-        <v>3777800</v>
+        <v>3728800</v>
       </c>
       <c r="G21" s="3">
-        <v>3800100</v>
+        <v>3750800</v>
       </c>
       <c r="H21" s="3">
-        <v>3659500</v>
+        <v>3611900</v>
       </c>
       <c r="I21" s="3">
-        <v>3524400</v>
+        <v>3478700</v>
       </c>
       <c r="J21" s="3">
-        <v>3762000</v>
+        <v>3713200</v>
       </c>
       <c r="K21" s="3">
         <v>3475200</v>
@@ -1236,25 +1236,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>226300</v>
+        <v>223300</v>
       </c>
       <c r="E22" s="3">
-        <v>202800</v>
+        <v>200200</v>
       </c>
       <c r="F22" s="3">
-        <v>203000</v>
+        <v>200300</v>
       </c>
       <c r="G22" s="3">
-        <v>214400</v>
+        <v>211600</v>
       </c>
       <c r="H22" s="3">
-        <v>228600</v>
+        <v>225600</v>
       </c>
       <c r="I22" s="3">
-        <v>232900</v>
+        <v>229900</v>
       </c>
       <c r="J22" s="3">
-        <v>259700</v>
+        <v>256300</v>
       </c>
       <c r="K22" s="3">
         <v>285600</v>
@@ -1278,25 +1278,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1458400</v>
+        <v>1439500</v>
       </c>
       <c r="E23" s="3">
-        <v>1523400</v>
+        <v>1503600</v>
       </c>
       <c r="F23" s="3">
-        <v>750800</v>
+        <v>741000</v>
       </c>
       <c r="G23" s="3">
-        <v>751700</v>
+        <v>742000</v>
       </c>
       <c r="H23" s="3">
-        <v>839900</v>
+        <v>829000</v>
       </c>
       <c r="I23" s="3">
-        <v>644500</v>
+        <v>636100</v>
       </c>
       <c r="J23" s="3">
-        <v>867800</v>
+        <v>856500</v>
       </c>
       <c r="K23" s="3">
         <v>532400</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>389900</v>
+        <v>384900</v>
       </c>
       <c r="E24" s="3">
-        <v>399600</v>
+        <v>394500</v>
       </c>
       <c r="F24" s="3">
-        <v>209200</v>
+        <v>206500</v>
       </c>
       <c r="G24" s="3">
-        <v>239000</v>
+        <v>235900</v>
       </c>
       <c r="H24" s="3">
-        <v>252900</v>
+        <v>249600</v>
       </c>
       <c r="I24" s="3">
-        <v>212100</v>
+        <v>209400</v>
       </c>
       <c r="J24" s="3">
-        <v>253500</v>
+        <v>250200</v>
       </c>
       <c r="K24" s="3">
         <v>169600</v>
@@ -1404,25 +1404,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1068500</v>
+        <v>1054600</v>
       </c>
       <c r="E26" s="3">
-        <v>1123700</v>
+        <v>1109100</v>
       </c>
       <c r="F26" s="3">
-        <v>541600</v>
+        <v>534600</v>
       </c>
       <c r="G26" s="3">
-        <v>512800</v>
+        <v>506100</v>
       </c>
       <c r="H26" s="3">
-        <v>587000</v>
+        <v>579400</v>
       </c>
       <c r="I26" s="3">
-        <v>432400</v>
+        <v>426800</v>
       </c>
       <c r="J26" s="3">
-        <v>614300</v>
+        <v>606400</v>
       </c>
       <c r="K26" s="3">
         <v>362800</v>
@@ -1446,25 +1446,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>972100</v>
+        <v>959500</v>
       </c>
       <c r="E27" s="3">
-        <v>1043000</v>
+        <v>1029400</v>
       </c>
       <c r="F27" s="3">
-        <v>506700</v>
+        <v>500100</v>
       </c>
       <c r="G27" s="3">
-        <v>474100</v>
+        <v>468000</v>
       </c>
       <c r="H27" s="3">
-        <v>530100</v>
+        <v>523200</v>
       </c>
       <c r="I27" s="3">
-        <v>367100</v>
+        <v>362300</v>
       </c>
       <c r="J27" s="3">
-        <v>614300</v>
+        <v>606400</v>
       </c>
       <c r="K27" s="3">
         <v>303900</v>
@@ -1548,7 +1548,7 @@
         <v>24</v>
       </c>
       <c r="J29" s="3">
-        <v>-66800</v>
+        <v>-65900</v>
       </c>
       <c r="K29" s="3">
         <v>105300</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100400</v>
+        <v>-99100</v>
       </c>
       <c r="E32" s="3">
-        <v>-339100</v>
+        <v>-334700</v>
       </c>
       <c r="F32" s="3">
-        <v>-136900</v>
+        <v>-135100</v>
       </c>
       <c r="G32" s="3">
-        <v>-69300</v>
+        <v>-68400</v>
       </c>
       <c r="H32" s="3">
-        <v>-38600</v>
+        <v>-38100</v>
       </c>
       <c r="I32" s="3">
-        <v>187400</v>
+        <v>184900</v>
       </c>
       <c r="J32" s="3">
-        <v>-59500</v>
+        <v>-58800</v>
       </c>
       <c r="K32" s="3">
         <v>22900</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>972100</v>
+        <v>959500</v>
       </c>
       <c r="E33" s="3">
-        <v>1043000</v>
+        <v>1029400</v>
       </c>
       <c r="F33" s="3">
-        <v>506700</v>
+        <v>500100</v>
       </c>
       <c r="G33" s="3">
-        <v>474100</v>
+        <v>468000</v>
       </c>
       <c r="H33" s="3">
-        <v>530100</v>
+        <v>523200</v>
       </c>
       <c r="I33" s="3">
-        <v>367100</v>
+        <v>362300</v>
       </c>
       <c r="J33" s="3">
-        <v>547500</v>
+        <v>540400</v>
       </c>
       <c r="K33" s="3">
         <v>409200</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>972100</v>
+        <v>959500</v>
       </c>
       <c r="E35" s="3">
-        <v>1043000</v>
+        <v>1029400</v>
       </c>
       <c r="F35" s="3">
-        <v>506700</v>
+        <v>500100</v>
       </c>
       <c r="G35" s="3">
-        <v>474100</v>
+        <v>468000</v>
       </c>
       <c r="H35" s="3">
-        <v>530100</v>
+        <v>523200</v>
       </c>
       <c r="I35" s="3">
-        <v>367100</v>
+        <v>362300</v>
       </c>
       <c r="J35" s="3">
-        <v>547500</v>
+        <v>540400</v>
       </c>
       <c r="K35" s="3">
         <v>409200</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1885800</v>
+        <v>1861300</v>
       </c>
       <c r="E41" s="3">
-        <v>2325100</v>
+        <v>2294900</v>
       </c>
       <c r="F41" s="3">
-        <v>2028700</v>
+        <v>2002300</v>
       </c>
       <c r="G41" s="3">
-        <v>1775500</v>
+        <v>1752500</v>
       </c>
       <c r="H41" s="3">
-        <v>2081600</v>
+        <v>2054600</v>
       </c>
       <c r="I41" s="3">
-        <v>1484700</v>
+        <v>1465400</v>
       </c>
       <c r="J41" s="3">
-        <v>2233200</v>
+        <v>2204200</v>
       </c>
       <c r="K41" s="3">
         <v>1894000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1018300</v>
+        <v>1005100</v>
       </c>
       <c r="E42" s="3">
-        <v>913000</v>
+        <v>901100</v>
       </c>
       <c r="F42" s="3">
-        <v>926200</v>
+        <v>914200</v>
       </c>
       <c r="G42" s="3">
-        <v>668700</v>
+        <v>660000</v>
       </c>
       <c r="H42" s="3">
-        <v>766000</v>
+        <v>756000</v>
       </c>
       <c r="I42" s="3">
-        <v>748900</v>
+        <v>739200</v>
       </c>
       <c r="J42" s="3">
-        <v>554800</v>
+        <v>547600</v>
       </c>
       <c r="K42" s="3">
         <v>216800</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4696700</v>
+        <v>4635700</v>
       </c>
       <c r="E43" s="3">
-        <v>3922000</v>
+        <v>3871000</v>
       </c>
       <c r="F43" s="3">
-        <v>3776500</v>
+        <v>3727400</v>
       </c>
       <c r="G43" s="3">
-        <v>4600400</v>
+        <v>4540700</v>
       </c>
       <c r="H43" s="3">
-        <v>4474800</v>
+        <v>4416700</v>
       </c>
       <c r="I43" s="3">
-        <v>4621400</v>
+        <v>4561400</v>
       </c>
       <c r="J43" s="3">
-        <v>4106700</v>
+        <v>4053300</v>
       </c>
       <c r="K43" s="3">
         <v>3617500</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>546100</v>
+        <v>539000</v>
       </c>
       <c r="E44" s="3">
-        <v>395900</v>
+        <v>390800</v>
       </c>
       <c r="F44" s="3">
-        <v>411700</v>
+        <v>406300</v>
       </c>
       <c r="G44" s="3">
-        <v>512400</v>
+        <v>505800</v>
       </c>
       <c r="H44" s="3">
-        <v>526700</v>
+        <v>519800</v>
       </c>
       <c r="I44" s="3">
-        <v>352400</v>
+        <v>347900</v>
       </c>
       <c r="J44" s="3">
-        <v>291000</v>
+        <v>287300</v>
       </c>
       <c r="K44" s="3">
         <v>388800</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1617900</v>
+        <v>1596900</v>
       </c>
       <c r="E45" s="3">
-        <v>1575000</v>
+        <v>1554600</v>
       </c>
       <c r="F45" s="3">
-        <v>1445700</v>
+        <v>1426900</v>
       </c>
       <c r="G45" s="3">
-        <v>1603800</v>
+        <v>1583000</v>
       </c>
       <c r="H45" s="3">
-        <v>1309400</v>
+        <v>1292400</v>
       </c>
       <c r="I45" s="3">
-        <v>240300</v>
+        <v>237200</v>
       </c>
       <c r="J45" s="3">
-        <v>239600</v>
+        <v>236500</v>
       </c>
       <c r="K45" s="3">
         <v>234500</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9764800</v>
+        <v>9638000</v>
       </c>
       <c r="E46" s="3">
-        <v>9130900</v>
+        <v>9012300</v>
       </c>
       <c r="F46" s="3">
-        <v>8588700</v>
+        <v>8477200</v>
       </c>
       <c r="G46" s="3">
-        <v>9160900</v>
+        <v>9041900</v>
       </c>
       <c r="H46" s="3">
-        <v>9158600</v>
+        <v>9039600</v>
       </c>
       <c r="I46" s="3">
-        <v>7447800</v>
+        <v>7351000</v>
       </c>
       <c r="J46" s="3">
-        <v>7425300</v>
+        <v>7328900</v>
       </c>
       <c r="K46" s="3">
         <v>6351600</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4214400</v>
+        <v>4159700</v>
       </c>
       <c r="E47" s="3">
-        <v>2465600</v>
+        <v>2433600</v>
       </c>
       <c r="F47" s="3">
-        <v>1811800</v>
+        <v>1788300</v>
       </c>
       <c r="G47" s="3">
-        <v>1748800</v>
+        <v>1726000</v>
       </c>
       <c r="H47" s="3">
-        <v>1338700</v>
+        <v>1321300</v>
       </c>
       <c r="I47" s="3">
-        <v>1434700</v>
+        <v>1416100</v>
       </c>
       <c r="J47" s="3">
-        <v>1276500</v>
+        <v>1259900</v>
       </c>
       <c r="K47" s="3">
         <v>1208000</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13849100</v>
+        <v>13669300</v>
       </c>
       <c r="E48" s="3">
-        <v>13424100</v>
+        <v>13249700</v>
       </c>
       <c r="F48" s="3">
-        <v>12929600</v>
+        <v>12761700</v>
       </c>
       <c r="G48" s="3">
-        <v>12659600</v>
+        <v>12495200</v>
       </c>
       <c r="H48" s="3">
-        <v>10902700</v>
+        <v>10761100</v>
       </c>
       <c r="I48" s="3">
-        <v>11358900</v>
+        <v>11211400</v>
       </c>
       <c r="J48" s="3">
-        <v>11904300</v>
+        <v>11749700</v>
       </c>
       <c r="K48" s="3">
         <v>11529900</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2410000</v>
+        <v>2378700</v>
       </c>
       <c r="E49" s="3">
-        <v>2654400</v>
+        <v>2620000</v>
       </c>
       <c r="F49" s="3">
-        <v>1664200</v>
+        <v>1642600</v>
       </c>
       <c r="G49" s="3">
-        <v>2182200</v>
+        <v>2153900</v>
       </c>
       <c r="H49" s="3">
-        <v>2623500</v>
+        <v>2589400</v>
       </c>
       <c r="I49" s="3">
-        <v>2027200</v>
+        <v>2000900</v>
       </c>
       <c r="J49" s="3">
-        <v>2327600</v>
+        <v>2297300</v>
       </c>
       <c r="K49" s="3">
         <v>1923800</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1316800</v>
+        <v>1299700</v>
       </c>
       <c r="E52" s="3">
-        <v>937600</v>
+        <v>925400</v>
       </c>
       <c r="F52" s="3">
-        <v>925800</v>
+        <v>913800</v>
       </c>
       <c r="G52" s="3">
-        <v>844400</v>
+        <v>833500</v>
       </c>
       <c r="H52" s="3">
-        <v>761900</v>
+        <v>752000</v>
       </c>
       <c r="I52" s="3">
-        <v>624200</v>
+        <v>616100</v>
       </c>
       <c r="J52" s="3">
-        <v>618800</v>
+        <v>610800</v>
       </c>
       <c r="K52" s="3">
         <v>699100</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31555100</v>
+        <v>31145300</v>
       </c>
       <c r="E54" s="3">
-        <v>28612700</v>
+        <v>28241100</v>
       </c>
       <c r="F54" s="3">
-        <v>25920200</v>
+        <v>25583500</v>
       </c>
       <c r="G54" s="3">
-        <v>26595900</v>
+        <v>26250500</v>
       </c>
       <c r="H54" s="3">
-        <v>24785400</v>
+        <v>24463500</v>
       </c>
       <c r="I54" s="3">
-        <v>22892800</v>
+        <v>22595500</v>
       </c>
       <c r="J54" s="3">
-        <v>23552600</v>
+        <v>23246700</v>
       </c>
       <c r="K54" s="3">
         <v>21712500</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>885900</v>
+        <v>874400</v>
       </c>
       <c r="E57" s="3">
-        <v>1183600</v>
+        <v>1168200</v>
       </c>
       <c r="F57" s="3">
-        <v>954600</v>
+        <v>942200</v>
       </c>
       <c r="G57" s="3">
-        <v>1004700</v>
+        <v>991600</v>
       </c>
       <c r="H57" s="3">
-        <v>952100</v>
+        <v>939700</v>
       </c>
       <c r="I57" s="3">
-        <v>1077500</v>
+        <v>1063500</v>
       </c>
       <c r="J57" s="3">
-        <v>951700</v>
+        <v>939300</v>
       </c>
       <c r="K57" s="3">
         <v>954900</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1650100</v>
+        <v>1628600</v>
       </c>
       <c r="E58" s="3">
-        <v>1589400</v>
+        <v>1568700</v>
       </c>
       <c r="F58" s="3">
-        <v>1357800</v>
+        <v>1340100</v>
       </c>
       <c r="G58" s="3">
-        <v>1215200</v>
+        <v>1199400</v>
       </c>
       <c r="H58" s="3">
-        <v>1053700</v>
+        <v>1040000</v>
       </c>
       <c r="I58" s="3">
-        <v>1211600</v>
+        <v>1195800</v>
       </c>
       <c r="J58" s="3">
-        <v>1401400</v>
+        <v>1383200</v>
       </c>
       <c r="K58" s="3">
         <v>1322600</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5702500</v>
+        <v>5628400</v>
       </c>
       <c r="E59" s="3">
-        <v>4982800</v>
+        <v>4918100</v>
       </c>
       <c r="F59" s="3">
-        <v>4765900</v>
+        <v>4704000</v>
       </c>
       <c r="G59" s="3">
-        <v>6388700</v>
+        <v>6305800</v>
       </c>
       <c r="H59" s="3">
-        <v>5222700</v>
+        <v>5154900</v>
       </c>
       <c r="I59" s="3">
-        <v>5006100</v>
+        <v>4941100</v>
       </c>
       <c r="J59" s="3">
-        <v>4935800</v>
+        <v>4871700</v>
       </c>
       <c r="K59" s="3">
         <v>4116100</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8238400</v>
+        <v>8131400</v>
       </c>
       <c r="E60" s="3">
-        <v>7755800</v>
+        <v>7655000</v>
       </c>
       <c r="F60" s="3">
-        <v>7078200</v>
+        <v>6986300</v>
       </c>
       <c r="G60" s="3">
-        <v>7814000</v>
+        <v>7712500</v>
       </c>
       <c r="H60" s="3">
-        <v>7228500</v>
+        <v>7134700</v>
       </c>
       <c r="I60" s="3">
-        <v>7295100</v>
+        <v>7200400</v>
       </c>
       <c r="J60" s="3">
-        <v>7288900</v>
+        <v>7194300</v>
       </c>
       <c r="K60" s="3">
         <v>6393500</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6957600</v>
+        <v>6867200</v>
       </c>
       <c r="E61" s="3">
-        <v>5800400</v>
+        <v>5725000</v>
       </c>
       <c r="F61" s="3">
-        <v>5156400</v>
+        <v>5089400</v>
       </c>
       <c r="G61" s="3">
-        <v>5337700</v>
+        <v>5268400</v>
       </c>
       <c r="H61" s="3">
-        <v>4065500</v>
+        <v>4012700</v>
       </c>
       <c r="I61" s="3">
-        <v>3934800</v>
+        <v>3883700</v>
       </c>
       <c r="J61" s="3">
-        <v>4851600</v>
+        <v>4788600</v>
       </c>
       <c r="K61" s="3">
         <v>5182800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2179800</v>
+        <v>2151500</v>
       </c>
       <c r="E62" s="3">
-        <v>2299800</v>
+        <v>2270000</v>
       </c>
       <c r="F62" s="3">
-        <v>1711000</v>
+        <v>1688800</v>
       </c>
       <c r="G62" s="3">
-        <v>2099000</v>
+        <v>2071700</v>
       </c>
       <c r="H62" s="3">
-        <v>2148300</v>
+        <v>2120400</v>
       </c>
       <c r="I62" s="3">
-        <v>1490700</v>
+        <v>1471300</v>
       </c>
       <c r="J62" s="3">
-        <v>1560000</v>
+        <v>1539800</v>
       </c>
       <c r="K62" s="3">
         <v>1133700</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>18763800</v>
+        <v>18520100</v>
       </c>
       <c r="E66" s="3">
-        <v>17080800</v>
+        <v>16858900</v>
       </c>
       <c r="F66" s="3">
-        <v>15131300</v>
+        <v>14934800</v>
       </c>
       <c r="G66" s="3">
-        <v>16075100</v>
+        <v>15866300</v>
       </c>
       <c r="H66" s="3">
-        <v>14619300</v>
+        <v>14429500</v>
       </c>
       <c r="I66" s="3">
-        <v>13792300</v>
+        <v>13613200</v>
       </c>
       <c r="J66" s="3">
-        <v>14742300</v>
+        <v>14550800</v>
       </c>
       <c r="K66" s="3">
         <v>13687100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10978200</v>
+        <v>10835600</v>
       </c>
       <c r="E72" s="3">
-        <v>10231300</v>
+        <v>10098400</v>
       </c>
       <c r="F72" s="3">
-        <v>9359700</v>
+        <v>9238100</v>
       </c>
       <c r="G72" s="3">
-        <v>8958000</v>
+        <v>8841700</v>
       </c>
       <c r="H72" s="3">
-        <v>8723200</v>
+        <v>8609900</v>
       </c>
       <c r="I72" s="3">
-        <v>7691100</v>
+        <v>7591200</v>
       </c>
       <c r="J72" s="3">
-        <v>7435500</v>
+        <v>7339000</v>
       </c>
       <c r="K72" s="3">
         <v>6703900</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12791400</v>
+        <v>12625300</v>
       </c>
       <c r="E76" s="3">
-        <v>11531900</v>
+        <v>11382200</v>
       </c>
       <c r="F76" s="3">
-        <v>10788800</v>
+        <v>10648700</v>
       </c>
       <c r="G76" s="3">
-        <v>10520800</v>
+        <v>10384200</v>
       </c>
       <c r="H76" s="3">
-        <v>10166100</v>
+        <v>10034000</v>
       </c>
       <c r="I76" s="3">
-        <v>9100500</v>
+        <v>8982300</v>
       </c>
       <c r="J76" s="3">
-        <v>8810300</v>
+        <v>8695900</v>
       </c>
       <c r="K76" s="3">
         <v>8025400</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>972100</v>
+        <v>959500</v>
       </c>
       <c r="E81" s="3">
-        <v>1043000</v>
+        <v>1029400</v>
       </c>
       <c r="F81" s="3">
-        <v>506700</v>
+        <v>500100</v>
       </c>
       <c r="G81" s="3">
-        <v>474100</v>
+        <v>468000</v>
       </c>
       <c r="H81" s="3">
-        <v>530100</v>
+        <v>523200</v>
       </c>
       <c r="I81" s="3">
-        <v>367100</v>
+        <v>362300</v>
       </c>
       <c r="J81" s="3">
-        <v>547500</v>
+        <v>540400</v>
       </c>
       <c r="K81" s="3">
         <v>409200</v>
@@ -3499,22 +3499,22 @@
         <v>24</v>
       </c>
       <c r="E83" s="3">
-        <v>2808500</v>
+        <v>2772000</v>
       </c>
       <c r="F83" s="3">
-        <v>2824100</v>
+        <v>2787400</v>
       </c>
       <c r="G83" s="3">
-        <v>2834000</v>
+        <v>2797200</v>
       </c>
       <c r="H83" s="3">
-        <v>2591000</v>
+        <v>2557400</v>
       </c>
       <c r="I83" s="3">
-        <v>2647000</v>
+        <v>2612600</v>
       </c>
       <c r="J83" s="3">
-        <v>2634600</v>
+        <v>2600300</v>
       </c>
       <c r="K83" s="3">
         <v>2693600</v>
@@ -3751,22 +3751,22 @@
         <v>24</v>
       </c>
       <c r="E89" s="3">
-        <v>4282600</v>
+        <v>4227000</v>
       </c>
       <c r="F89" s="3">
-        <v>3649700</v>
+        <v>3602300</v>
       </c>
       <c r="G89" s="3">
-        <v>2883800</v>
+        <v>2846300</v>
       </c>
       <c r="H89" s="3">
-        <v>3088100</v>
+        <v>3048000</v>
       </c>
       <c r="I89" s="3">
-        <v>2985900</v>
+        <v>2947100</v>
       </c>
       <c r="J89" s="3">
-        <v>3673500</v>
+        <v>3625800</v>
       </c>
       <c r="K89" s="3">
         <v>3130200</v>
@@ -3811,22 +3811,22 @@
         <v>24</v>
       </c>
       <c r="E91" s="3">
-        <v>-2694400</v>
+        <v>-2659500</v>
       </c>
       <c r="F91" s="3">
-        <v>-2474300</v>
+        <v>-2442200</v>
       </c>
       <c r="G91" s="3">
-        <v>-2517600</v>
+        <v>-2484900</v>
       </c>
       <c r="H91" s="3">
-        <v>-1740900</v>
+        <v>-1718300</v>
       </c>
       <c r="I91" s="3">
-        <v>-1880500</v>
+        <v>-1856100</v>
       </c>
       <c r="J91" s="3">
-        <v>-2128500</v>
+        <v>-2100900</v>
       </c>
       <c r="K91" s="3">
         <v>-2305600</v>
@@ -3937,22 +3937,22 @@
         <v>24</v>
       </c>
       <c r="E94" s="3">
-        <v>-3955900</v>
+        <v>-3904500</v>
       </c>
       <c r="F94" s="3">
-        <v>-2896300</v>
+        <v>-2858700</v>
       </c>
       <c r="G94" s="3">
-        <v>-2993400</v>
+        <v>-2954500</v>
       </c>
       <c r="H94" s="3">
-        <v>-2082200</v>
+        <v>-2055100</v>
       </c>
       <c r="I94" s="3">
-        <v>-2682100</v>
+        <v>-2647300</v>
       </c>
       <c r="J94" s="3">
-        <v>-2683400</v>
+        <v>-2648600</v>
       </c>
       <c r="K94" s="3">
         <v>-1777400</v>
@@ -3997,22 +3997,22 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-269800</v>
+        <v>-266300</v>
       </c>
       <c r="F96" s="3">
-        <v>-239100</v>
+        <v>-236000</v>
       </c>
       <c r="G96" s="3">
-        <v>-235000</v>
+        <v>-231900</v>
       </c>
       <c r="H96" s="3">
-        <v>-229900</v>
+        <v>-227000</v>
       </c>
       <c r="I96" s="3">
-        <v>-187200</v>
+        <v>-184800</v>
       </c>
       <c r="J96" s="3">
-        <v>-141800</v>
+        <v>-139900</v>
       </c>
       <c r="K96" s="3">
         <v>-30800</v>
@@ -4165,22 +4165,22 @@
         <v>24</v>
       </c>
       <c r="E100" s="3">
-        <v>-31800</v>
+        <v>-31400</v>
       </c>
       <c r="F100" s="3">
-        <v>-498600</v>
+        <v>-492200</v>
       </c>
       <c r="G100" s="3">
-        <v>-192300</v>
+        <v>-189800</v>
       </c>
       <c r="H100" s="3">
-        <v>-409400</v>
+        <v>-404100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1049900</v>
+        <v>-1036300</v>
       </c>
       <c r="J100" s="3">
-        <v>-726300</v>
+        <v>-716900</v>
       </c>
       <c r="K100" s="3">
         <v>-861400</v>
@@ -4207,7 +4207,7 @@
         <v>24</v>
       </c>
       <c r="E101" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F101" s="3">
         <v>-1600</v>
@@ -4249,22 +4249,22 @@
         <v>24</v>
       </c>
       <c r="E102" s="3">
-        <v>296400</v>
+        <v>292600</v>
       </c>
       <c r="F102" s="3">
-        <v>253100</v>
+        <v>249800</v>
       </c>
       <c r="G102" s="3">
-        <v>-306100</v>
+        <v>-302100</v>
       </c>
       <c r="H102" s="3">
-        <v>596900</v>
+        <v>589200</v>
       </c>
       <c r="I102" s="3">
-        <v>-748500</v>
+        <v>-738800</v>
       </c>
       <c r="J102" s="3">
-        <v>262500</v>
+        <v>259000</v>
       </c>
       <c r="K102" s="3">
         <v>496400</v>

--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>KT</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19494000</v>
+        <v>19254700</v>
       </c>
       <c r="E8" s="3">
-        <v>18922500</v>
+        <v>18724500</v>
       </c>
       <c r="F8" s="3">
-        <v>18176700</v>
+        <v>18175500</v>
       </c>
       <c r="G8" s="3">
-        <v>18500000</v>
+        <v>17459200</v>
       </c>
       <c r="H8" s="3">
-        <v>17829700</v>
+        <v>17769700</v>
       </c>
       <c r="I8" s="3">
-        <v>17774300</v>
+        <v>17125900</v>
       </c>
       <c r="J8" s="3">
+        <v>17072700</v>
+      </c>
+      <c r="K8" s="3">
         <v>17285200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16488100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18741800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21892700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20700800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19879000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7287500</v>
+        <v>6858900</v>
       </c>
       <c r="E9" s="3">
-        <v>7512000</v>
+        <v>6999800</v>
       </c>
       <c r="F9" s="3">
-        <v>7338600</v>
+        <v>7215500</v>
       </c>
       <c r="G9" s="3">
-        <v>7742900</v>
+        <v>7048900</v>
       </c>
       <c r="H9" s="3">
-        <v>7175300</v>
+        <v>7437300</v>
       </c>
       <c r="I9" s="3">
-        <v>7025600</v>
+        <v>6892100</v>
       </c>
       <c r="J9" s="3">
+        <v>6748300</v>
+      </c>
+      <c r="K9" s="3">
         <v>6724800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6518700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7504500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6253800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5936900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6602100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12206500</v>
+        <v>12395700</v>
       </c>
       <c r="E10" s="3">
-        <v>11410500</v>
+        <v>11724700</v>
       </c>
       <c r="F10" s="3">
-        <v>10838100</v>
+        <v>10960100</v>
       </c>
       <c r="G10" s="3">
-        <v>10757000</v>
+        <v>10410300</v>
       </c>
       <c r="H10" s="3">
-        <v>10654400</v>
+        <v>10332400</v>
       </c>
       <c r="I10" s="3">
-        <v>10748700</v>
+        <v>10233800</v>
       </c>
       <c r="J10" s="3">
+        <v>10324400</v>
+      </c>
+      <c r="K10" s="3">
         <v>10560400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9969400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11237300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15638900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14763900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13277000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>133000</v>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E12" s="3">
-        <v>128400</v>
+        <v>127700</v>
       </c>
       <c r="F12" s="3">
-        <v>119300</v>
+        <v>123300</v>
       </c>
       <c r="G12" s="3">
-        <v>125400</v>
+        <v>114600</v>
       </c>
       <c r="H12" s="3">
-        <v>134300</v>
+        <v>120500</v>
       </c>
       <c r="I12" s="3">
-        <v>128200</v>
+        <v>129000</v>
       </c>
       <c r="J12" s="3">
+        <v>123100</v>
+      </c>
+      <c r="K12" s="3">
         <v>127600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>136000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>161300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>156000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>257300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>277000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-279200</v>
+        <v>40600</v>
       </c>
       <c r="E14" s="3">
-        <v>-98500</v>
+        <v>-268200</v>
       </c>
       <c r="F14" s="3">
-        <v>93700</v>
+        <v>-94600</v>
       </c>
       <c r="G14" s="3">
-        <v>-3900</v>
+        <v>90000</v>
       </c>
       <c r="H14" s="3">
-        <v>-57800</v>
+        <v>-3700</v>
       </c>
       <c r="I14" s="3">
-        <v>-5700</v>
+        <v>-55500</v>
       </c>
       <c r="J14" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K14" s="3">
         <v>40300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>115900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>89900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>39300</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2778500</v>
+        <v>2781400</v>
       </c>
       <c r="E15" s="3">
-        <v>2741800</v>
+        <v>2668800</v>
       </c>
       <c r="F15" s="3">
-        <v>2762100</v>
+        <v>2633600</v>
       </c>
       <c r="G15" s="3">
-        <v>2758400</v>
+        <v>2653000</v>
       </c>
       <c r="H15" s="3">
-        <v>2494100</v>
+        <v>2649500</v>
       </c>
       <c r="I15" s="3">
-        <v>2557000</v>
+        <v>2395700</v>
       </c>
       <c r="J15" s="3">
+        <v>2456100</v>
+      </c>
+      <c r="K15" s="3">
         <v>2542400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2470600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2793600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3245200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2750200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2661700</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>17930300</v>
+        <v>18090900</v>
       </c>
       <c r="E17" s="3">
-        <v>17553400</v>
+        <v>17222500</v>
       </c>
       <c r="F17" s="3">
-        <v>17370400</v>
+        <v>16860500</v>
       </c>
       <c r="G17" s="3">
-        <v>17614800</v>
+        <v>16684700</v>
       </c>
       <c r="H17" s="3">
-        <v>16813200</v>
+        <v>16919500</v>
       </c>
       <c r="I17" s="3">
-        <v>16723400</v>
+        <v>16149500</v>
       </c>
       <c r="J17" s="3">
+        <v>16063200</v>
+      </c>
+      <c r="K17" s="3">
         <v>16231100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15647200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19173300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21603000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19292300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18090700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1563700</v>
+        <v>1163800</v>
       </c>
       <c r="E18" s="3">
-        <v>1369100</v>
+        <v>1502000</v>
       </c>
       <c r="F18" s="3">
-        <v>806200</v>
+        <v>1315000</v>
       </c>
       <c r="G18" s="3">
-        <v>885100</v>
+        <v>774400</v>
       </c>
       <c r="H18" s="3">
-        <v>1016500</v>
+        <v>850200</v>
       </c>
       <c r="I18" s="3">
-        <v>1051000</v>
+        <v>976400</v>
       </c>
       <c r="J18" s="3">
+        <v>1009500</v>
+      </c>
+      <c r="K18" s="3">
         <v>1054100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>840900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-431500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>289700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1408400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1788400</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>99100</v>
+        <v>62900</v>
       </c>
       <c r="E20" s="3">
-        <v>334700</v>
+        <v>95200</v>
       </c>
       <c r="F20" s="3">
-        <v>135100</v>
+        <v>321500</v>
       </c>
       <c r="G20" s="3">
-        <v>68400</v>
+        <v>129800</v>
       </c>
       <c r="H20" s="3">
-        <v>38100</v>
+        <v>65700</v>
       </c>
       <c r="I20" s="3">
-        <v>-184900</v>
+        <v>36600</v>
       </c>
       <c r="J20" s="3">
+        <v>-177600</v>
+      </c>
+      <c r="K20" s="3">
         <v>58800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-22900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-285500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>85400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>177300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>92500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="3">
+        <v>4050200</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="3">
-        <v>4475800</v>
-      </c>
       <c r="F21" s="3">
-        <v>3728800</v>
+        <v>4299100</v>
       </c>
       <c r="G21" s="3">
-        <v>3750800</v>
+        <v>3581600</v>
       </c>
       <c r="H21" s="3">
-        <v>3611900</v>
+        <v>3602700</v>
       </c>
       <c r="I21" s="3">
-        <v>3478700</v>
+        <v>3469400</v>
       </c>
       <c r="J21" s="3">
+        <v>3341300</v>
+      </c>
+      <c r="K21" s="3">
         <v>3713200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3475200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2521100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3633700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4402500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4547700</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>223300</v>
+        <v>260100</v>
       </c>
       <c r="E22" s="3">
-        <v>200200</v>
+        <v>214500</v>
       </c>
       <c r="F22" s="3">
-        <v>200300</v>
+        <v>192300</v>
       </c>
       <c r="G22" s="3">
-        <v>211600</v>
+        <v>192400</v>
       </c>
       <c r="H22" s="3">
-        <v>225600</v>
+        <v>203300</v>
       </c>
       <c r="I22" s="3">
-        <v>229900</v>
+        <v>216700</v>
       </c>
       <c r="J22" s="3">
+        <v>220800</v>
+      </c>
+      <c r="K22" s="3">
         <v>256300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>285600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>399100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>409800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>397300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>432500</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1439500</v>
+        <v>966600</v>
       </c>
       <c r="E23" s="3">
-        <v>1503600</v>
+        <v>1382700</v>
       </c>
       <c r="F23" s="3">
-        <v>741000</v>
+        <v>1444200</v>
       </c>
       <c r="G23" s="3">
-        <v>742000</v>
+        <v>711800</v>
       </c>
       <c r="H23" s="3">
-        <v>829000</v>
+        <v>712700</v>
       </c>
       <c r="I23" s="3">
-        <v>636100</v>
+        <v>796200</v>
       </c>
       <c r="J23" s="3">
+        <v>611000</v>
+      </c>
+      <c r="K23" s="3">
         <v>856500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>532400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1116000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-34700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1188500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1448300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>384900</v>
+        <v>244800</v>
       </c>
       <c r="E24" s="3">
-        <v>394500</v>
+        <v>369700</v>
       </c>
       <c r="F24" s="3">
-        <v>206500</v>
+        <v>378900</v>
       </c>
       <c r="G24" s="3">
-        <v>235900</v>
+        <v>198300</v>
       </c>
       <c r="H24" s="3">
-        <v>249600</v>
+        <v>226500</v>
       </c>
       <c r="I24" s="3">
-        <v>209400</v>
+        <v>239800</v>
       </c>
       <c r="J24" s="3">
+        <v>201100</v>
+      </c>
+      <c r="K24" s="3">
         <v>250200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>169600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-231800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>45100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>233400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>286600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1054600</v>
+        <v>721800</v>
       </c>
       <c r="E26" s="3">
-        <v>1109100</v>
+        <v>1013000</v>
       </c>
       <c r="F26" s="3">
-        <v>534600</v>
+        <v>1065400</v>
       </c>
       <c r="G26" s="3">
-        <v>506100</v>
+        <v>513500</v>
       </c>
       <c r="H26" s="3">
-        <v>579400</v>
+        <v>486100</v>
       </c>
       <c r="I26" s="3">
-        <v>426800</v>
+        <v>556500</v>
       </c>
       <c r="J26" s="3">
+        <v>409900</v>
+      </c>
+      <c r="K26" s="3">
         <v>606400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>362800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-884200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-79800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>955100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1161700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>959500</v>
+        <v>736400</v>
       </c>
       <c r="E27" s="3">
-        <v>1029400</v>
+        <v>921600</v>
       </c>
       <c r="F27" s="3">
-        <v>500100</v>
+        <v>988800</v>
       </c>
       <c r="G27" s="3">
-        <v>468000</v>
+        <v>480400</v>
       </c>
       <c r="H27" s="3">
-        <v>523200</v>
+        <v>449500</v>
       </c>
       <c r="I27" s="3">
-        <v>362300</v>
+        <v>502600</v>
       </c>
       <c r="J27" s="3">
+        <v>348000</v>
+      </c>
+      <c r="K27" s="3">
         <v>606400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>303900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-939900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-172800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>905200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1152000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1547,27 +1607,30 @@
       <c r="I29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3">
         <v>-65900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>105300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>53700</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-26500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>148400</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-99100</v>
+        <v>-62900</v>
       </c>
       <c r="E32" s="3">
-        <v>-334700</v>
+        <v>-95200</v>
       </c>
       <c r="F32" s="3">
-        <v>-135100</v>
+        <v>-321500</v>
       </c>
       <c r="G32" s="3">
-        <v>-68400</v>
+        <v>-129800</v>
       </c>
       <c r="H32" s="3">
-        <v>-38100</v>
+        <v>-65700</v>
       </c>
       <c r="I32" s="3">
-        <v>184900</v>
+        <v>-36600</v>
       </c>
       <c r="J32" s="3">
+        <v>177600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-58800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>22900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>285500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-85400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-177300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-92500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>959500</v>
+        <v>736400</v>
       </c>
       <c r="E33" s="3">
-        <v>1029400</v>
+        <v>921600</v>
       </c>
       <c r="F33" s="3">
-        <v>500100</v>
+        <v>988800</v>
       </c>
       <c r="G33" s="3">
-        <v>468000</v>
+        <v>480400</v>
       </c>
       <c r="H33" s="3">
-        <v>523200</v>
+        <v>449500</v>
       </c>
       <c r="I33" s="3">
-        <v>362300</v>
+        <v>502600</v>
       </c>
       <c r="J33" s="3">
+        <v>348000</v>
+      </c>
+      <c r="K33" s="3">
         <v>540400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>409200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-886200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-172800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>878700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1300400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>959500</v>
+        <v>736400</v>
       </c>
       <c r="E35" s="3">
-        <v>1029400</v>
+        <v>921600</v>
       </c>
       <c r="F35" s="3">
-        <v>500100</v>
+        <v>988800</v>
       </c>
       <c r="G35" s="3">
-        <v>468000</v>
+        <v>480400</v>
       </c>
       <c r="H35" s="3">
-        <v>523200</v>
+        <v>449500</v>
       </c>
       <c r="I35" s="3">
-        <v>362300</v>
+        <v>502600</v>
       </c>
       <c r="J35" s="3">
+        <v>348000</v>
+      </c>
+      <c r="K35" s="3">
         <v>540400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>409200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-886200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-172800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>878700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1300400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1861300</v>
+        <v>2065900</v>
       </c>
       <c r="E41" s="3">
-        <v>2294900</v>
+        <v>1787800</v>
       </c>
       <c r="F41" s="3">
-        <v>2002300</v>
+        <v>2204300</v>
       </c>
       <c r="G41" s="3">
-        <v>1752500</v>
+        <v>1923300</v>
       </c>
       <c r="H41" s="3">
-        <v>2054600</v>
+        <v>1683300</v>
       </c>
       <c r="I41" s="3">
-        <v>1465400</v>
+        <v>1973500</v>
       </c>
       <c r="J41" s="3">
+        <v>1407600</v>
+      </c>
+      <c r="K41" s="3">
         <v>2204200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1894000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1586500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1884500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2454100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>597300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1005100</v>
+        <v>1051300</v>
       </c>
       <c r="E42" s="3">
-        <v>901100</v>
+        <v>965400</v>
       </c>
       <c r="F42" s="3">
-        <v>914200</v>
+        <v>865500</v>
       </c>
       <c r="G42" s="3">
-        <v>660000</v>
+        <v>878100</v>
       </c>
       <c r="H42" s="3">
-        <v>756000</v>
+        <v>633900</v>
       </c>
       <c r="I42" s="3">
-        <v>739200</v>
+        <v>726200</v>
       </c>
       <c r="J42" s="3">
+        <v>710000</v>
+      </c>
+      <c r="K42" s="3">
         <v>547600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>216800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>279500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>436900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1708200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1515700</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4635700</v>
+        <v>5236700</v>
       </c>
       <c r="E43" s="3">
-        <v>3871000</v>
+        <v>4452700</v>
       </c>
       <c r="F43" s="3">
-        <v>3727400</v>
+        <v>3718200</v>
       </c>
       <c r="G43" s="3">
-        <v>4540700</v>
+        <v>3580300</v>
       </c>
       <c r="H43" s="3">
-        <v>4416700</v>
+        <v>4361400</v>
       </c>
       <c r="I43" s="3">
-        <v>4561400</v>
+        <v>4242400</v>
       </c>
       <c r="J43" s="3">
+        <v>4381300</v>
+      </c>
+      <c r="K43" s="3">
         <v>4053300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3617500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4858500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5831100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7453300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5811000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>539000</v>
+        <v>666000</v>
       </c>
       <c r="E44" s="3">
-        <v>390800</v>
+        <v>517700</v>
       </c>
       <c r="F44" s="3">
-        <v>406300</v>
+        <v>375300</v>
       </c>
       <c r="G44" s="3">
-        <v>505800</v>
+        <v>390300</v>
       </c>
       <c r="H44" s="3">
-        <v>519800</v>
+        <v>485800</v>
       </c>
       <c r="I44" s="3">
-        <v>347900</v>
+        <v>499300</v>
       </c>
       <c r="J44" s="3">
+        <v>334100</v>
+      </c>
+      <c r="K44" s="3">
         <v>287300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>388800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>351900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>613000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1346800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>607300</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1596900</v>
+        <v>1578300</v>
       </c>
       <c r="E45" s="3">
-        <v>1554600</v>
+        <v>1533900</v>
       </c>
       <c r="F45" s="3">
-        <v>1426900</v>
+        <v>1493200</v>
       </c>
       <c r="G45" s="3">
-        <v>1583000</v>
+        <v>1370600</v>
       </c>
       <c r="H45" s="3">
-        <v>1292400</v>
+        <v>1520500</v>
       </c>
       <c r="I45" s="3">
-        <v>237200</v>
+        <v>1241400</v>
       </c>
       <c r="J45" s="3">
+        <v>227800</v>
+      </c>
+      <c r="K45" s="3">
         <v>236500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>234500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>293700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>309000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>305200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>280300</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9638000</v>
+        <v>10598300</v>
       </c>
       <c r="E46" s="3">
-        <v>9012300</v>
+        <v>9257500</v>
       </c>
       <c r="F46" s="3">
-        <v>8477200</v>
+        <v>8656600</v>
       </c>
       <c r="G46" s="3">
-        <v>9041900</v>
+        <v>8142600</v>
       </c>
       <c r="H46" s="3">
-        <v>9039600</v>
+        <v>8685000</v>
       </c>
       <c r="I46" s="3">
-        <v>7351000</v>
+        <v>8682800</v>
       </c>
       <c r="J46" s="3">
+        <v>7060900</v>
+      </c>
+      <c r="K46" s="3">
         <v>7328900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6351600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7370000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9074400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8834600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8811600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4159700</v>
+        <v>4150600</v>
       </c>
       <c r="E47" s="3">
-        <v>2433600</v>
+        <v>3995500</v>
       </c>
       <c r="F47" s="3">
-        <v>1788300</v>
+        <v>2337600</v>
       </c>
       <c r="G47" s="3">
-        <v>1726000</v>
+        <v>1717700</v>
       </c>
       <c r="H47" s="3">
-        <v>1321300</v>
+        <v>1657900</v>
       </c>
       <c r="I47" s="3">
-        <v>1416100</v>
+        <v>1269200</v>
       </c>
       <c r="J47" s="3">
+        <v>1360200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1259900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1208000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2354300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2525800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3649000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3468200</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13669300</v>
+        <v>13413900</v>
       </c>
       <c r="E48" s="3">
-        <v>13249700</v>
+        <v>13129700</v>
       </c>
       <c r="F48" s="3">
-        <v>12761700</v>
+        <v>12726700</v>
       </c>
       <c r="G48" s="3">
-        <v>12495200</v>
+        <v>12258000</v>
       </c>
       <c r="H48" s="3">
-        <v>10761100</v>
+        <v>12002000</v>
       </c>
       <c r="I48" s="3">
-        <v>11211400</v>
+        <v>10336300</v>
       </c>
       <c r="J48" s="3">
+        <v>10768900</v>
+      </c>
+      <c r="K48" s="3">
         <v>11749700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11529900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14723400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15918100</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13663600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2378700</v>
+        <v>1849700</v>
       </c>
       <c r="E49" s="3">
-        <v>2620000</v>
+        <v>2284800</v>
       </c>
       <c r="F49" s="3">
-        <v>1642600</v>
+        <v>2516600</v>
       </c>
       <c r="G49" s="3">
-        <v>2153900</v>
+        <v>1577700</v>
       </c>
       <c r="H49" s="3">
-        <v>2589400</v>
+        <v>2068800</v>
       </c>
       <c r="I49" s="3">
-        <v>2000900</v>
+        <v>2487200</v>
       </c>
       <c r="J49" s="3">
+        <v>1921900</v>
+      </c>
+      <c r="K49" s="3">
         <v>2297300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1923800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2977000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3482900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5398000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2379100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1299700</v>
+        <v>1165800</v>
       </c>
       <c r="E52" s="3">
-        <v>925400</v>
+        <v>1248400</v>
       </c>
       <c r="F52" s="3">
-        <v>913800</v>
+        <v>888900</v>
       </c>
       <c r="G52" s="3">
-        <v>833500</v>
+        <v>877700</v>
       </c>
       <c r="H52" s="3">
-        <v>752000</v>
+        <v>800600</v>
       </c>
       <c r="I52" s="3">
-        <v>616100</v>
+        <v>722400</v>
       </c>
       <c r="J52" s="3">
+        <v>591800</v>
+      </c>
+      <c r="K52" s="3">
         <v>610800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>699100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>966700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>712300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>593000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>554300</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31145300</v>
+        <v>31178300</v>
       </c>
       <c r="E54" s="3">
-        <v>28241100</v>
+        <v>29915900</v>
       </c>
       <c r="F54" s="3">
-        <v>25583500</v>
+        <v>27126300</v>
       </c>
       <c r="G54" s="3">
-        <v>26250500</v>
+        <v>24573700</v>
       </c>
       <c r="H54" s="3">
-        <v>24463500</v>
+        <v>25214300</v>
       </c>
       <c r="I54" s="3">
-        <v>22595500</v>
+        <v>23497800</v>
       </c>
       <c r="J54" s="3">
+        <v>21703600</v>
+      </c>
+      <c r="K54" s="3">
         <v>23246700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21712500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28391400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31713600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29028600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28876900</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>874400</v>
+        <v>947400</v>
       </c>
       <c r="E57" s="3">
-        <v>1168200</v>
+        <v>839900</v>
       </c>
       <c r="F57" s="3">
-        <v>942200</v>
+        <v>1122100</v>
       </c>
       <c r="G57" s="3">
-        <v>991600</v>
+        <v>905000</v>
       </c>
       <c r="H57" s="3">
-        <v>939700</v>
+        <v>952500</v>
       </c>
       <c r="I57" s="3">
-        <v>1063500</v>
+        <v>902600</v>
       </c>
       <c r="J57" s="3">
+        <v>1021500</v>
+      </c>
+      <c r="K57" s="3">
         <v>939300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>954900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1008000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1562200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1531200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1471800</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1628600</v>
+        <v>2457500</v>
       </c>
       <c r="E58" s="3">
-        <v>1568700</v>
+        <v>1564300</v>
       </c>
       <c r="F58" s="3">
-        <v>1340100</v>
+        <v>1506800</v>
       </c>
       <c r="G58" s="3">
-        <v>1199400</v>
+        <v>1287200</v>
       </c>
       <c r="H58" s="3">
-        <v>1040000</v>
+        <v>1152100</v>
       </c>
       <c r="I58" s="3">
-        <v>1195800</v>
+        <v>999000</v>
       </c>
       <c r="J58" s="3">
+        <v>1148600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1383200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1322600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2499700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2766600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2697300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1942700</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5628400</v>
+        <v>6192800</v>
       </c>
       <c r="E59" s="3">
-        <v>4918100</v>
+        <v>5406200</v>
       </c>
       <c r="F59" s="3">
-        <v>4704000</v>
+        <v>4723900</v>
       </c>
       <c r="G59" s="3">
-        <v>6305800</v>
+        <v>4518300</v>
       </c>
       <c r="H59" s="3">
-        <v>5154900</v>
+        <v>6056900</v>
       </c>
       <c r="I59" s="3">
-        <v>4941100</v>
+        <v>4951400</v>
       </c>
       <c r="J59" s="3">
+        <v>4746000</v>
+      </c>
+      <c r="K59" s="3">
         <v>4871700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4116100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4881500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5885200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5235600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4456100</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8131400</v>
+        <v>9597600</v>
       </c>
       <c r="E60" s="3">
-        <v>7655000</v>
+        <v>7810500</v>
       </c>
       <c r="F60" s="3">
-        <v>6986300</v>
+        <v>7352900</v>
       </c>
       <c r="G60" s="3">
-        <v>7712500</v>
+        <v>6710500</v>
       </c>
       <c r="H60" s="3">
-        <v>7134700</v>
+        <v>7408100</v>
       </c>
       <c r="I60" s="3">
-        <v>7200400</v>
+        <v>6853000</v>
       </c>
       <c r="J60" s="3">
+        <v>6916100</v>
+      </c>
+      <c r="K60" s="3">
         <v>7194300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6393500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8389200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10213900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9464100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7870600</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6867200</v>
+        <v>5863100</v>
       </c>
       <c r="E61" s="3">
-        <v>5725000</v>
+        <v>6596100</v>
       </c>
       <c r="F61" s="3">
-        <v>5089400</v>
+        <v>5499100</v>
       </c>
       <c r="G61" s="3">
-        <v>5268400</v>
+        <v>4888500</v>
       </c>
       <c r="H61" s="3">
-        <v>4012700</v>
+        <v>5060400</v>
       </c>
       <c r="I61" s="3">
-        <v>3883700</v>
+        <v>3854300</v>
       </c>
       <c r="J61" s="3">
+        <v>3730400</v>
+      </c>
+      <c r="K61" s="3">
         <v>4788600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5182800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8311500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7745800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6944000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8078500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2151500</v>
+        <v>2167900</v>
       </c>
       <c r="E62" s="3">
-        <v>2270000</v>
+        <v>2066600</v>
       </c>
       <c r="F62" s="3">
-        <v>1688800</v>
+        <v>2180400</v>
       </c>
       <c r="G62" s="3">
-        <v>2071700</v>
+        <v>1622100</v>
       </c>
       <c r="H62" s="3">
-        <v>2120400</v>
+        <v>1990000</v>
       </c>
       <c r="I62" s="3">
-        <v>1471300</v>
+        <v>2036700</v>
       </c>
       <c r="J62" s="3">
+        <v>1413300</v>
+      </c>
+      <c r="K62" s="3">
         <v>1539800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1133700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1789200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2071800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1517400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1643700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>18520100</v>
+        <v>18951400</v>
       </c>
       <c r="E66" s="3">
-        <v>16858900</v>
+        <v>17789000</v>
       </c>
       <c r="F66" s="3">
-        <v>14934800</v>
+        <v>16193400</v>
       </c>
       <c r="G66" s="3">
-        <v>15866300</v>
+        <v>14345300</v>
       </c>
       <c r="H66" s="3">
-        <v>14429500</v>
+        <v>15240000</v>
       </c>
       <c r="I66" s="3">
-        <v>13613200</v>
+        <v>13859900</v>
       </c>
       <c r="J66" s="3">
+        <v>13075800</v>
+      </c>
+      <c r="K66" s="3">
         <v>14550800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13687100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19707300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21041400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18688900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18343100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10835600</v>
+        <v>10580900</v>
       </c>
       <c r="E72" s="3">
-        <v>10098400</v>
+        <v>10407900</v>
       </c>
       <c r="F72" s="3">
-        <v>9238100</v>
+        <v>9699800</v>
       </c>
       <c r="G72" s="3">
-        <v>8841700</v>
+        <v>8873500</v>
       </c>
       <c r="H72" s="3">
-        <v>8609900</v>
+        <v>8492700</v>
       </c>
       <c r="I72" s="3">
-        <v>7591200</v>
+        <v>8270100</v>
       </c>
       <c r="J72" s="3">
+        <v>7291500</v>
+      </c>
+      <c r="K72" s="3">
         <v>7339000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6703900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7197500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9117600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17885900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9197700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12625300</v>
+        <v>12226900</v>
       </c>
       <c r="E76" s="3">
-        <v>11382200</v>
+        <v>12126900</v>
       </c>
       <c r="F76" s="3">
-        <v>10648700</v>
+        <v>10932900</v>
       </c>
       <c r="G76" s="3">
-        <v>10384200</v>
+        <v>10228400</v>
       </c>
       <c r="H76" s="3">
-        <v>10034000</v>
+        <v>9974300</v>
       </c>
       <c r="I76" s="3">
-        <v>8982300</v>
+        <v>9638000</v>
       </c>
       <c r="J76" s="3">
+        <v>8627800</v>
+      </c>
+      <c r="K76" s="3">
         <v>8695900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8025400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8684100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10672200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10339700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10533800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>959500</v>
+        <v>736400</v>
       </c>
       <c r="E81" s="3">
-        <v>1029400</v>
+        <v>921600</v>
       </c>
       <c r="F81" s="3">
-        <v>500100</v>
+        <v>988800</v>
       </c>
       <c r="G81" s="3">
-        <v>468000</v>
+        <v>480400</v>
       </c>
       <c r="H81" s="3">
-        <v>523200</v>
+        <v>449500</v>
       </c>
       <c r="I81" s="3">
-        <v>362300</v>
+        <v>502600</v>
       </c>
       <c r="J81" s="3">
+        <v>348000</v>
+      </c>
+      <c r="K81" s="3">
         <v>540400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>409200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-886200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-172800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>878700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1300400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="3">
+        <v>2823500</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E83" s="3">
-        <v>2772000</v>
-      </c>
       <c r="F83" s="3">
-        <v>2787400</v>
+        <v>2662600</v>
       </c>
       <c r="G83" s="3">
-        <v>2797200</v>
+        <v>2677400</v>
       </c>
       <c r="H83" s="3">
-        <v>2557400</v>
+        <v>2686800</v>
       </c>
       <c r="I83" s="3">
-        <v>2612600</v>
+        <v>2456400</v>
       </c>
       <c r="J83" s="3">
+        <v>2509500</v>
+      </c>
+      <c r="K83" s="3">
         <v>2600300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2693600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3238000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3294900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2783600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2696800</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="3">
+        <v>4017400</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E89" s="3">
-        <v>4227000</v>
-      </c>
       <c r="F89" s="3">
-        <v>3602300</v>
+        <v>4060100</v>
       </c>
       <c r="G89" s="3">
-        <v>2846300</v>
+        <v>3460100</v>
       </c>
       <c r="H89" s="3">
-        <v>3048000</v>
+        <v>2734000</v>
       </c>
       <c r="I89" s="3">
-        <v>2947100</v>
+        <v>2927600</v>
       </c>
       <c r="J89" s="3">
+        <v>2830800</v>
+      </c>
+      <c r="K89" s="3">
         <v>3625800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3130200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1609800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3741100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4809400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1947600</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="3">
+        <v>-2696600</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E91" s="3">
-        <v>-2659500</v>
-      </c>
       <c r="F91" s="3">
-        <v>-2442200</v>
+        <v>-2554500</v>
       </c>
       <c r="G91" s="3">
-        <v>-2484900</v>
+        <v>-2345800</v>
       </c>
       <c r="H91" s="3">
-        <v>-1718300</v>
+        <v>-2386800</v>
       </c>
       <c r="I91" s="3">
-        <v>-1856100</v>
+        <v>-1650400</v>
       </c>
       <c r="J91" s="3">
+        <v>-1782800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2100900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2305600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2396400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2810200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3158600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3155000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="3">
+        <v>-3373000</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E94" s="3">
-        <v>-3904500</v>
-      </c>
       <c r="F94" s="3">
-        <v>-2858700</v>
+        <v>-3750400</v>
       </c>
       <c r="G94" s="3">
-        <v>-2954500</v>
+        <v>-2745900</v>
       </c>
       <c r="H94" s="3">
-        <v>-2055100</v>
+        <v>-2837900</v>
       </c>
       <c r="I94" s="3">
-        <v>-2647300</v>
+        <v>-1974000</v>
       </c>
       <c r="J94" s="3">
+        <v>-2542800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2648600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1777400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2663600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3442200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3235000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2399100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-384600</v>
       </c>
       <c r="E96" s="3">
-        <v>-266300</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-236000</v>
+        <v>-255700</v>
       </c>
       <c r="G96" s="3">
-        <v>-231900</v>
+        <v>-226700</v>
       </c>
       <c r="H96" s="3">
-        <v>-227000</v>
+        <v>-222800</v>
       </c>
       <c r="I96" s="3">
-        <v>-184800</v>
+        <v>-218000</v>
       </c>
       <c r="J96" s="3">
+        <v>-177500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-139900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-30800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-187100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-465300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-827100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1063400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="3">
+        <v>-330500</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E100" s="3">
-        <v>-31400</v>
-      </c>
       <c r="F100" s="3">
-        <v>-492200</v>
+        <v>-30100</v>
       </c>
       <c r="G100" s="3">
-        <v>-189800</v>
+        <v>-472700</v>
       </c>
       <c r="H100" s="3">
-        <v>-404100</v>
+        <v>-182300</v>
       </c>
       <c r="I100" s="3">
-        <v>-1036300</v>
+        <v>-388100</v>
       </c>
       <c r="J100" s="3">
+        <v>-995400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-716900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-861400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>900200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-283700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1073400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>695200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
-        <v>-1600</v>
-      </c>
       <c r="G101" s="3">
-        <v>-4200</v>
+        <v>-1500</v>
       </c>
       <c r="H101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
-        <v>-2400</v>
-      </c>
       <c r="J101" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>11500</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="3">
+        <v>314300</v>
+      </c>
+      <c r="E102" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E102" s="3">
-        <v>292600</v>
-      </c>
       <c r="F102" s="3">
-        <v>249800</v>
+        <v>281000</v>
       </c>
       <c r="G102" s="3">
-        <v>-302100</v>
+        <v>240000</v>
       </c>
       <c r="H102" s="3">
-        <v>589200</v>
+        <v>-290200</v>
       </c>
       <c r="I102" s="3">
-        <v>-738800</v>
+        <v>565900</v>
       </c>
       <c r="J102" s="3">
+        <v>-709700</v>
+      </c>
+      <c r="K102" s="3">
         <v>259000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>496400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-153100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>255200</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19254700</v>
+        <v>19782200</v>
       </c>
       <c r="E8" s="3">
-        <v>18724500</v>
+        <v>19237500</v>
       </c>
       <c r="F8" s="3">
-        <v>18175500</v>
+        <v>18673500</v>
       </c>
       <c r="G8" s="3">
-        <v>17459200</v>
+        <v>17937500</v>
       </c>
       <c r="H8" s="3">
-        <v>17769700</v>
+        <v>18256500</v>
       </c>
       <c r="I8" s="3">
-        <v>17125900</v>
+        <v>17595100</v>
       </c>
       <c r="J8" s="3">
-        <v>17072700</v>
+        <v>17540500</v>
       </c>
       <c r="K8" s="3">
         <v>17285200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6858900</v>
+        <v>7046900</v>
       </c>
       <c r="E9" s="3">
-        <v>6999800</v>
+        <v>7191600</v>
       </c>
       <c r="F9" s="3">
-        <v>7215500</v>
+        <v>7413200</v>
       </c>
       <c r="G9" s="3">
-        <v>7048900</v>
+        <v>7242000</v>
       </c>
       <c r="H9" s="3">
-        <v>7437300</v>
+        <v>7641100</v>
       </c>
       <c r="I9" s="3">
-        <v>6892100</v>
+        <v>7080900</v>
       </c>
       <c r="J9" s="3">
-        <v>6748300</v>
+        <v>6933200</v>
       </c>
       <c r="K9" s="3">
         <v>6724800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12395700</v>
+        <v>12735300</v>
       </c>
       <c r="E10" s="3">
-        <v>11724700</v>
+        <v>12045900</v>
       </c>
       <c r="F10" s="3">
-        <v>10960100</v>
+        <v>11260300</v>
       </c>
       <c r="G10" s="3">
-        <v>10410300</v>
+        <v>10695500</v>
       </c>
       <c r="H10" s="3">
-        <v>10332400</v>
+        <v>10615500</v>
       </c>
       <c r="I10" s="3">
-        <v>10233800</v>
+        <v>10514200</v>
       </c>
       <c r="J10" s="3">
-        <v>10324400</v>
+        <v>10607300</v>
       </c>
       <c r="K10" s="3">
         <v>10560400</v>
@@ -883,22 +883,22 @@
         <v>24</v>
       </c>
       <c r="E12" s="3">
-        <v>127700</v>
+        <v>131200</v>
       </c>
       <c r="F12" s="3">
-        <v>123300</v>
+        <v>126700</v>
       </c>
       <c r="G12" s="3">
-        <v>114600</v>
+        <v>117700</v>
       </c>
       <c r="H12" s="3">
-        <v>120500</v>
+        <v>123800</v>
       </c>
       <c r="I12" s="3">
-        <v>129000</v>
+        <v>132600</v>
       </c>
       <c r="J12" s="3">
-        <v>123100</v>
+        <v>126500</v>
       </c>
       <c r="K12" s="3">
         <v>127600</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>40600</v>
+        <v>41700</v>
       </c>
       <c r="E14" s="3">
-        <v>-268200</v>
+        <v>-275600</v>
       </c>
       <c r="F14" s="3">
-        <v>-94600</v>
+        <v>-97200</v>
       </c>
       <c r="G14" s="3">
-        <v>90000</v>
+        <v>92400</v>
       </c>
       <c r="H14" s="3">
-        <v>-3700</v>
+        <v>-3800</v>
       </c>
       <c r="I14" s="3">
-        <v>-55500</v>
+        <v>-57000</v>
       </c>
       <c r="J14" s="3">
-        <v>-5500</v>
+        <v>-5700</v>
       </c>
       <c r="K14" s="3">
         <v>40300</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2781400</v>
+        <v>2857600</v>
       </c>
       <c r="E15" s="3">
-        <v>2668800</v>
+        <v>2741900</v>
       </c>
       <c r="F15" s="3">
-        <v>2633600</v>
+        <v>2705700</v>
       </c>
       <c r="G15" s="3">
-        <v>2653000</v>
+        <v>2725700</v>
       </c>
       <c r="H15" s="3">
-        <v>2649500</v>
+        <v>2722100</v>
       </c>
       <c r="I15" s="3">
-        <v>2395700</v>
+        <v>2461300</v>
       </c>
       <c r="J15" s="3">
-        <v>2456100</v>
+        <v>2523400</v>
       </c>
       <c r="K15" s="3">
         <v>2542400</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>18090900</v>
+        <v>18586500</v>
       </c>
       <c r="E17" s="3">
-        <v>17222500</v>
+        <v>17694400</v>
       </c>
       <c r="F17" s="3">
-        <v>16860500</v>
+        <v>17322400</v>
       </c>
       <c r="G17" s="3">
-        <v>16684700</v>
+        <v>17141900</v>
       </c>
       <c r="H17" s="3">
-        <v>16919500</v>
+        <v>17383100</v>
       </c>
       <c r="I17" s="3">
-        <v>16149500</v>
+        <v>16592000</v>
       </c>
       <c r="J17" s="3">
-        <v>16063200</v>
+        <v>16503300</v>
       </c>
       <c r="K17" s="3">
         <v>16231100</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1163800</v>
+        <v>1195700</v>
       </c>
       <c r="E18" s="3">
-        <v>1502000</v>
+        <v>1543100</v>
       </c>
       <c r="F18" s="3">
-        <v>1315000</v>
+        <v>1351100</v>
       </c>
       <c r="G18" s="3">
-        <v>774400</v>
+        <v>795600</v>
       </c>
       <c r="H18" s="3">
-        <v>850200</v>
+        <v>873500</v>
       </c>
       <c r="I18" s="3">
-        <v>976400</v>
+        <v>1003100</v>
       </c>
       <c r="J18" s="3">
-        <v>1009500</v>
+        <v>1037100</v>
       </c>
       <c r="K18" s="3">
         <v>1054100</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>62900</v>
+        <v>64700</v>
       </c>
       <c r="E20" s="3">
-        <v>95200</v>
+        <v>97800</v>
       </c>
       <c r="F20" s="3">
-        <v>321500</v>
+        <v>330300</v>
       </c>
       <c r="G20" s="3">
-        <v>129800</v>
+        <v>133300</v>
       </c>
       <c r="H20" s="3">
-        <v>65700</v>
+        <v>67500</v>
       </c>
       <c r="I20" s="3">
-        <v>36600</v>
+        <v>37600</v>
       </c>
       <c r="J20" s="3">
-        <v>-177600</v>
+        <v>-182500</v>
       </c>
       <c r="K20" s="3">
         <v>58800</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>4050200</v>
+        <v>4161200</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F21" s="3">
-        <v>4299100</v>
+        <v>4416900</v>
       </c>
       <c r="G21" s="3">
-        <v>3581600</v>
+        <v>3679700</v>
       </c>
       <c r="H21" s="3">
-        <v>3602700</v>
+        <v>3701400</v>
       </c>
       <c r="I21" s="3">
-        <v>3469400</v>
+        <v>3564400</v>
       </c>
       <c r="J21" s="3">
-        <v>3341300</v>
+        <v>3432900</v>
       </c>
       <c r="K21" s="3">
         <v>3713200</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>260100</v>
+        <v>267300</v>
       </c>
       <c r="E22" s="3">
-        <v>214500</v>
+        <v>220400</v>
       </c>
       <c r="F22" s="3">
-        <v>192300</v>
+        <v>197500</v>
       </c>
       <c r="G22" s="3">
-        <v>192400</v>
+        <v>197700</v>
       </c>
       <c r="H22" s="3">
-        <v>203300</v>
+        <v>208800</v>
       </c>
       <c r="I22" s="3">
-        <v>216700</v>
+        <v>222700</v>
       </c>
       <c r="J22" s="3">
-        <v>220800</v>
+        <v>226800</v>
       </c>
       <c r="K22" s="3">
         <v>256300</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>966600</v>
+        <v>993100</v>
       </c>
       <c r="E23" s="3">
-        <v>1382700</v>
+        <v>1420600</v>
       </c>
       <c r="F23" s="3">
-        <v>1444200</v>
+        <v>1483800</v>
       </c>
       <c r="G23" s="3">
-        <v>711800</v>
+        <v>731300</v>
       </c>
       <c r="H23" s="3">
-        <v>712700</v>
+        <v>732200</v>
       </c>
       <c r="I23" s="3">
-        <v>796200</v>
+        <v>818100</v>
       </c>
       <c r="J23" s="3">
-        <v>611000</v>
+        <v>627800</v>
       </c>
       <c r="K23" s="3">
         <v>856500</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>244800</v>
+        <v>251500</v>
       </c>
       <c r="E24" s="3">
-        <v>369700</v>
+        <v>379800</v>
       </c>
       <c r="F24" s="3">
-        <v>378900</v>
+        <v>389300</v>
       </c>
       <c r="G24" s="3">
-        <v>198300</v>
+        <v>203700</v>
       </c>
       <c r="H24" s="3">
-        <v>226500</v>
+        <v>232700</v>
       </c>
       <c r="I24" s="3">
-        <v>239800</v>
+        <v>246300</v>
       </c>
       <c r="J24" s="3">
-        <v>201100</v>
+        <v>206600</v>
       </c>
       <c r="K24" s="3">
         <v>250200</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>721800</v>
+        <v>741500</v>
       </c>
       <c r="E26" s="3">
-        <v>1013000</v>
+        <v>1040700</v>
       </c>
       <c r="F26" s="3">
-        <v>1065400</v>
+        <v>1094500</v>
       </c>
       <c r="G26" s="3">
-        <v>513500</v>
+        <v>527500</v>
       </c>
       <c r="H26" s="3">
-        <v>486100</v>
+        <v>499500</v>
       </c>
       <c r="I26" s="3">
-        <v>556500</v>
+        <v>571700</v>
       </c>
       <c r="J26" s="3">
-        <v>409900</v>
+        <v>421100</v>
       </c>
       <c r="K26" s="3">
         <v>606400</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>736400</v>
+        <v>756500</v>
       </c>
       <c r="E27" s="3">
-        <v>921600</v>
+        <v>946900</v>
       </c>
       <c r="F27" s="3">
-        <v>988800</v>
+        <v>1015900</v>
       </c>
       <c r="G27" s="3">
-        <v>480400</v>
+        <v>493500</v>
       </c>
       <c r="H27" s="3">
-        <v>449500</v>
+        <v>461800</v>
       </c>
       <c r="I27" s="3">
-        <v>502600</v>
+        <v>516300</v>
       </c>
       <c r="J27" s="3">
-        <v>348000</v>
+        <v>357600</v>
       </c>
       <c r="K27" s="3">
         <v>606400</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-62900</v>
+        <v>-64700</v>
       </c>
       <c r="E32" s="3">
-        <v>-95200</v>
+        <v>-97800</v>
       </c>
       <c r="F32" s="3">
-        <v>-321500</v>
+        <v>-330300</v>
       </c>
       <c r="G32" s="3">
-        <v>-129800</v>
+        <v>-133300</v>
       </c>
       <c r="H32" s="3">
-        <v>-65700</v>
+        <v>-67500</v>
       </c>
       <c r="I32" s="3">
-        <v>-36600</v>
+        <v>-37600</v>
       </c>
       <c r="J32" s="3">
-        <v>177600</v>
+        <v>182500</v>
       </c>
       <c r="K32" s="3">
         <v>-58800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>736400</v>
+        <v>756500</v>
       </c>
       <c r="E33" s="3">
-        <v>921600</v>
+        <v>946900</v>
       </c>
       <c r="F33" s="3">
-        <v>988800</v>
+        <v>1015900</v>
       </c>
       <c r="G33" s="3">
-        <v>480400</v>
+        <v>493500</v>
       </c>
       <c r="H33" s="3">
-        <v>449500</v>
+        <v>461800</v>
       </c>
       <c r="I33" s="3">
-        <v>502600</v>
+        <v>516300</v>
       </c>
       <c r="J33" s="3">
-        <v>348000</v>
+        <v>357600</v>
       </c>
       <c r="K33" s="3">
         <v>540400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>736400</v>
+        <v>756500</v>
       </c>
       <c r="E35" s="3">
-        <v>921600</v>
+        <v>946900</v>
       </c>
       <c r="F35" s="3">
-        <v>988800</v>
+        <v>1015900</v>
       </c>
       <c r="G35" s="3">
-        <v>480400</v>
+        <v>493500</v>
       </c>
       <c r="H35" s="3">
-        <v>449500</v>
+        <v>461800</v>
       </c>
       <c r="I35" s="3">
-        <v>502600</v>
+        <v>516300</v>
       </c>
       <c r="J35" s="3">
-        <v>348000</v>
+        <v>357600</v>
       </c>
       <c r="K35" s="3">
         <v>540400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2065900</v>
+        <v>2122500</v>
       </c>
       <c r="E41" s="3">
-        <v>1787800</v>
+        <v>1836800</v>
       </c>
       <c r="F41" s="3">
-        <v>2204300</v>
+        <v>2264700</v>
       </c>
       <c r="G41" s="3">
-        <v>1923300</v>
+        <v>1976000</v>
       </c>
       <c r="H41" s="3">
-        <v>1683300</v>
+        <v>1729400</v>
       </c>
       <c r="I41" s="3">
-        <v>1973500</v>
+        <v>2027600</v>
       </c>
       <c r="J41" s="3">
-        <v>1407600</v>
+        <v>1446100</v>
       </c>
       <c r="K41" s="3">
         <v>2204200</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1051300</v>
+        <v>1080200</v>
       </c>
       <c r="E42" s="3">
-        <v>965400</v>
+        <v>991800</v>
       </c>
       <c r="F42" s="3">
-        <v>865500</v>
+        <v>889200</v>
       </c>
       <c r="G42" s="3">
-        <v>878100</v>
+        <v>902100</v>
       </c>
       <c r="H42" s="3">
-        <v>633900</v>
+        <v>651300</v>
       </c>
       <c r="I42" s="3">
-        <v>726200</v>
+        <v>746100</v>
       </c>
       <c r="J42" s="3">
-        <v>710000</v>
+        <v>729500</v>
       </c>
       <c r="K42" s="3">
         <v>547600</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5236700</v>
+        <v>5380200</v>
       </c>
       <c r="E43" s="3">
-        <v>4452700</v>
+        <v>4574700</v>
       </c>
       <c r="F43" s="3">
-        <v>3718200</v>
+        <v>3820100</v>
       </c>
       <c r="G43" s="3">
-        <v>3580300</v>
+        <v>3678400</v>
       </c>
       <c r="H43" s="3">
-        <v>4361400</v>
+        <v>4480900</v>
       </c>
       <c r="I43" s="3">
-        <v>4242400</v>
+        <v>4358600</v>
       </c>
       <c r="J43" s="3">
-        <v>4381300</v>
+        <v>4501300</v>
       </c>
       <c r="K43" s="3">
         <v>4053300</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>666000</v>
+        <v>684200</v>
       </c>
       <c r="E44" s="3">
-        <v>517700</v>
+        <v>531900</v>
       </c>
       <c r="F44" s="3">
-        <v>375300</v>
+        <v>385600</v>
       </c>
       <c r="G44" s="3">
-        <v>390300</v>
+        <v>401000</v>
       </c>
       <c r="H44" s="3">
-        <v>485800</v>
+        <v>499100</v>
       </c>
       <c r="I44" s="3">
-        <v>499300</v>
+        <v>513000</v>
       </c>
       <c r="J44" s="3">
-        <v>334100</v>
+        <v>343300</v>
       </c>
       <c r="K44" s="3">
         <v>287300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1578300</v>
+        <v>1621600</v>
       </c>
       <c r="E45" s="3">
-        <v>1533900</v>
+        <v>1575900</v>
       </c>
       <c r="F45" s="3">
-        <v>1493200</v>
+        <v>1534100</v>
       </c>
       <c r="G45" s="3">
-        <v>1370600</v>
+        <v>1408200</v>
       </c>
       <c r="H45" s="3">
-        <v>1520500</v>
+        <v>1562200</v>
       </c>
       <c r="I45" s="3">
-        <v>1241400</v>
+        <v>1275400</v>
       </c>
       <c r="J45" s="3">
-        <v>227800</v>
+        <v>234100</v>
       </c>
       <c r="K45" s="3">
         <v>236500</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10598300</v>
+        <v>10888600</v>
       </c>
       <c r="E46" s="3">
-        <v>9257500</v>
+        <v>9511100</v>
       </c>
       <c r="F46" s="3">
-        <v>8656600</v>
+        <v>8893800</v>
       </c>
       <c r="G46" s="3">
-        <v>8142600</v>
+        <v>8365600</v>
       </c>
       <c r="H46" s="3">
-        <v>8685000</v>
+        <v>8922900</v>
       </c>
       <c r="I46" s="3">
-        <v>8682800</v>
+        <v>8920700</v>
       </c>
       <c r="J46" s="3">
-        <v>7060900</v>
+        <v>7254300</v>
       </c>
       <c r="K46" s="3">
         <v>7328900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4150600</v>
+        <v>4264400</v>
       </c>
       <c r="E47" s="3">
-        <v>3995500</v>
+        <v>4104900</v>
       </c>
       <c r="F47" s="3">
-        <v>2337600</v>
+        <v>2401600</v>
       </c>
       <c r="G47" s="3">
-        <v>1717700</v>
+        <v>1764700</v>
       </c>
       <c r="H47" s="3">
-        <v>1657900</v>
+        <v>1703300</v>
       </c>
       <c r="I47" s="3">
-        <v>1269200</v>
+        <v>1303900</v>
       </c>
       <c r="J47" s="3">
-        <v>1360200</v>
+        <v>1397400</v>
       </c>
       <c r="K47" s="3">
         <v>1259900</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13413900</v>
+        <v>13781400</v>
       </c>
       <c r="E48" s="3">
-        <v>13129700</v>
+        <v>13489400</v>
       </c>
       <c r="F48" s="3">
-        <v>12726700</v>
+        <v>13075400</v>
       </c>
       <c r="G48" s="3">
-        <v>12258000</v>
+        <v>12593800</v>
       </c>
       <c r="H48" s="3">
-        <v>12002000</v>
+        <v>12330800</v>
       </c>
       <c r="I48" s="3">
-        <v>10336300</v>
+        <v>10619500</v>
       </c>
       <c r="J48" s="3">
-        <v>10768900</v>
+        <v>11063900</v>
       </c>
       <c r="K48" s="3">
         <v>11749700</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1849700</v>
+        <v>1900400</v>
       </c>
       <c r="E49" s="3">
-        <v>2284800</v>
+        <v>2347400</v>
       </c>
       <c r="F49" s="3">
-        <v>2516600</v>
+        <v>2585500</v>
       </c>
       <c r="G49" s="3">
-        <v>1577700</v>
+        <v>1620900</v>
       </c>
       <c r="H49" s="3">
-        <v>2068800</v>
+        <v>2125500</v>
       </c>
       <c r="I49" s="3">
-        <v>2487200</v>
+        <v>2555300</v>
       </c>
       <c r="J49" s="3">
-        <v>1921900</v>
+        <v>1974500</v>
       </c>
       <c r="K49" s="3">
         <v>2297300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1165800</v>
+        <v>1197700</v>
       </c>
       <c r="E52" s="3">
-        <v>1248400</v>
+        <v>1282600</v>
       </c>
       <c r="F52" s="3">
-        <v>888900</v>
+        <v>913300</v>
       </c>
       <c r="G52" s="3">
-        <v>877700</v>
+        <v>901800</v>
       </c>
       <c r="H52" s="3">
-        <v>800600</v>
+        <v>822500</v>
       </c>
       <c r="I52" s="3">
-        <v>722400</v>
+        <v>742200</v>
       </c>
       <c r="J52" s="3">
-        <v>591800</v>
+        <v>608000</v>
       </c>
       <c r="K52" s="3">
         <v>610800</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31178300</v>
+        <v>32032500</v>
       </c>
       <c r="E54" s="3">
-        <v>29915900</v>
+        <v>30735500</v>
       </c>
       <c r="F54" s="3">
-        <v>27126300</v>
+        <v>27869500</v>
       </c>
       <c r="G54" s="3">
-        <v>24573700</v>
+        <v>25246900</v>
       </c>
       <c r="H54" s="3">
-        <v>25214300</v>
+        <v>25905100</v>
       </c>
       <c r="I54" s="3">
-        <v>23497800</v>
+        <v>24141600</v>
       </c>
       <c r="J54" s="3">
-        <v>21703600</v>
+        <v>22298200</v>
       </c>
       <c r="K54" s="3">
         <v>23246700</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>947400</v>
+        <v>973300</v>
       </c>
       <c r="E57" s="3">
-        <v>839900</v>
+        <v>862900</v>
       </c>
       <c r="F57" s="3">
-        <v>1122100</v>
+        <v>1152900</v>
       </c>
       <c r="G57" s="3">
-        <v>905000</v>
+        <v>929800</v>
       </c>
       <c r="H57" s="3">
-        <v>952500</v>
+        <v>978600</v>
       </c>
       <c r="I57" s="3">
-        <v>902600</v>
+        <v>927400</v>
       </c>
       <c r="J57" s="3">
-        <v>1021500</v>
+        <v>1049500</v>
       </c>
       <c r="K57" s="3">
         <v>939300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2457500</v>
+        <v>2524800</v>
       </c>
       <c r="E58" s="3">
-        <v>1564300</v>
+        <v>1607200</v>
       </c>
       <c r="F58" s="3">
-        <v>1506800</v>
+        <v>1548100</v>
       </c>
       <c r="G58" s="3">
-        <v>1287200</v>
+        <v>1322500</v>
       </c>
       <c r="H58" s="3">
-        <v>1152100</v>
+        <v>1183600</v>
       </c>
       <c r="I58" s="3">
-        <v>999000</v>
+        <v>1026400</v>
       </c>
       <c r="J58" s="3">
-        <v>1148600</v>
+        <v>1180100</v>
       </c>
       <c r="K58" s="3">
         <v>1383200</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6192800</v>
+        <v>6362400</v>
       </c>
       <c r="E59" s="3">
-        <v>5406200</v>
+        <v>5554400</v>
       </c>
       <c r="F59" s="3">
-        <v>4723900</v>
+        <v>4853400</v>
       </c>
       <c r="G59" s="3">
-        <v>4518300</v>
+        <v>4642100</v>
       </c>
       <c r="H59" s="3">
-        <v>6056900</v>
+        <v>6222800</v>
       </c>
       <c r="I59" s="3">
-        <v>4951400</v>
+        <v>5087100</v>
       </c>
       <c r="J59" s="3">
-        <v>4746000</v>
+        <v>4876100</v>
       </c>
       <c r="K59" s="3">
         <v>4871700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9597600</v>
+        <v>9860600</v>
       </c>
       <c r="E60" s="3">
-        <v>7810500</v>
+        <v>8024500</v>
       </c>
       <c r="F60" s="3">
-        <v>7352900</v>
+        <v>7554300</v>
       </c>
       <c r="G60" s="3">
-        <v>6710500</v>
+        <v>6894400</v>
       </c>
       <c r="H60" s="3">
-        <v>7408100</v>
+        <v>7611000</v>
       </c>
       <c r="I60" s="3">
-        <v>6853000</v>
+        <v>7040800</v>
       </c>
       <c r="J60" s="3">
-        <v>6916100</v>
+        <v>7105600</v>
       </c>
       <c r="K60" s="3">
         <v>7194300</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5863100</v>
+        <v>6023700</v>
       </c>
       <c r="E61" s="3">
-        <v>6596100</v>
+        <v>6776800</v>
       </c>
       <c r="F61" s="3">
-        <v>5499100</v>
+        <v>5649700</v>
       </c>
       <c r="G61" s="3">
-        <v>4888500</v>
+        <v>5022400</v>
       </c>
       <c r="H61" s="3">
-        <v>5060400</v>
+        <v>5199000</v>
       </c>
       <c r="I61" s="3">
-        <v>3854300</v>
+        <v>3959900</v>
       </c>
       <c r="J61" s="3">
-        <v>3730400</v>
+        <v>3832600</v>
       </c>
       <c r="K61" s="3">
         <v>4788600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2167900</v>
+        <v>2227300</v>
       </c>
       <c r="E62" s="3">
-        <v>2066600</v>
+        <v>2123200</v>
       </c>
       <c r="F62" s="3">
-        <v>2180400</v>
+        <v>2240100</v>
       </c>
       <c r="G62" s="3">
-        <v>1622100</v>
+        <v>1666500</v>
       </c>
       <c r="H62" s="3">
-        <v>1990000</v>
+        <v>2044500</v>
       </c>
       <c r="I62" s="3">
-        <v>2036700</v>
+        <v>2092500</v>
       </c>
       <c r="J62" s="3">
-        <v>1413300</v>
+        <v>1452000</v>
       </c>
       <c r="K62" s="3">
         <v>1539800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>18951400</v>
+        <v>19470600</v>
       </c>
       <c r="E66" s="3">
-        <v>17789000</v>
+        <v>18276400</v>
       </c>
       <c r="F66" s="3">
-        <v>16193400</v>
+        <v>16637100</v>
       </c>
       <c r="G66" s="3">
-        <v>14345300</v>
+        <v>14738300</v>
       </c>
       <c r="H66" s="3">
-        <v>15240000</v>
+        <v>15657500</v>
       </c>
       <c r="I66" s="3">
-        <v>13859900</v>
+        <v>14239600</v>
       </c>
       <c r="J66" s="3">
-        <v>13075800</v>
+        <v>13434100</v>
       </c>
       <c r="K66" s="3">
         <v>14550800</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10580900</v>
+        <v>10870800</v>
       </c>
       <c r="E72" s="3">
-        <v>10407900</v>
+        <v>10693000</v>
       </c>
       <c r="F72" s="3">
-        <v>9699800</v>
+        <v>9965500</v>
       </c>
       <c r="G72" s="3">
-        <v>8873500</v>
+        <v>9116600</v>
       </c>
       <c r="H72" s="3">
-        <v>8492700</v>
+        <v>8725300</v>
       </c>
       <c r="I72" s="3">
-        <v>8270100</v>
+        <v>8496600</v>
       </c>
       <c r="J72" s="3">
-        <v>7291500</v>
+        <v>7491300</v>
       </c>
       <c r="K72" s="3">
         <v>7339000</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12226900</v>
+        <v>12561900</v>
       </c>
       <c r="E76" s="3">
-        <v>12126900</v>
+        <v>12459100</v>
       </c>
       <c r="F76" s="3">
-        <v>10932900</v>
+        <v>11232400</v>
       </c>
       <c r="G76" s="3">
-        <v>10228400</v>
+        <v>10508600</v>
       </c>
       <c r="H76" s="3">
-        <v>9974300</v>
+        <v>10247500</v>
       </c>
       <c r="I76" s="3">
-        <v>9638000</v>
+        <v>9902000</v>
       </c>
       <c r="J76" s="3">
-        <v>8627800</v>
+        <v>8864100</v>
       </c>
       <c r="K76" s="3">
         <v>8695900</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>736400</v>
+        <v>756500</v>
       </c>
       <c r="E81" s="3">
-        <v>921600</v>
+        <v>946900</v>
       </c>
       <c r="F81" s="3">
-        <v>988800</v>
+        <v>1015900</v>
       </c>
       <c r="G81" s="3">
-        <v>480400</v>
+        <v>493500</v>
       </c>
       <c r="H81" s="3">
-        <v>449500</v>
+        <v>461800</v>
       </c>
       <c r="I81" s="3">
-        <v>502600</v>
+        <v>516300</v>
       </c>
       <c r="J81" s="3">
-        <v>348000</v>
+        <v>357600</v>
       </c>
       <c r="K81" s="3">
         <v>540400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2823500</v>
+        <v>2900800</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F83" s="3">
-        <v>2662600</v>
+        <v>2735500</v>
       </c>
       <c r="G83" s="3">
-        <v>2677400</v>
+        <v>2750700</v>
       </c>
       <c r="H83" s="3">
-        <v>2686800</v>
+        <v>2760400</v>
       </c>
       <c r="I83" s="3">
-        <v>2456400</v>
+        <v>2523700</v>
       </c>
       <c r="J83" s="3">
-        <v>2509500</v>
+        <v>2578300</v>
       </c>
       <c r="K83" s="3">
         <v>2600300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4017400</v>
+        <v>4127500</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F89" s="3">
-        <v>4060100</v>
+        <v>4171400</v>
       </c>
       <c r="G89" s="3">
-        <v>3460100</v>
+        <v>3554900</v>
       </c>
       <c r="H89" s="3">
-        <v>2734000</v>
+        <v>2808900</v>
       </c>
       <c r="I89" s="3">
-        <v>2927600</v>
+        <v>3007800</v>
       </c>
       <c r="J89" s="3">
-        <v>2830800</v>
+        <v>2908300</v>
       </c>
       <c r="K89" s="3">
         <v>3625800</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2696600</v>
+        <v>-2770500</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F91" s="3">
-        <v>-2554500</v>
+        <v>-2624500</v>
       </c>
       <c r="G91" s="3">
-        <v>-2345800</v>
+        <v>-2410000</v>
       </c>
       <c r="H91" s="3">
-        <v>-2386800</v>
+        <v>-2452200</v>
       </c>
       <c r="I91" s="3">
-        <v>-1650400</v>
+        <v>-1695700</v>
       </c>
       <c r="J91" s="3">
-        <v>-1782800</v>
+        <v>-1831700</v>
       </c>
       <c r="K91" s="3">
         <v>-2100900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3373000</v>
+        <v>-3465400</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F94" s="3">
-        <v>-3750400</v>
+        <v>-3853100</v>
       </c>
       <c r="G94" s="3">
-        <v>-2745900</v>
+        <v>-2821100</v>
       </c>
       <c r="H94" s="3">
-        <v>-2837900</v>
+        <v>-2915600</v>
       </c>
       <c r="I94" s="3">
-        <v>-1974000</v>
+        <v>-2028100</v>
       </c>
       <c r="J94" s="3">
-        <v>-2542800</v>
+        <v>-2612400</v>
       </c>
       <c r="K94" s="3">
         <v>-2648600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-384600</v>
+        <v>-395100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-255700</v>
+        <v>-262800</v>
       </c>
       <c r="G96" s="3">
-        <v>-226700</v>
+        <v>-232900</v>
       </c>
       <c r="H96" s="3">
-        <v>-222800</v>
+        <v>-228900</v>
       </c>
       <c r="I96" s="3">
-        <v>-218000</v>
+        <v>-224000</v>
       </c>
       <c r="J96" s="3">
-        <v>-177500</v>
+        <v>-182400</v>
       </c>
       <c r="K96" s="3">
         <v>-139900</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-330500</v>
+        <v>-339600</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F100" s="3">
-        <v>-30100</v>
+        <v>-31000</v>
       </c>
       <c r="G100" s="3">
-        <v>-472700</v>
+        <v>-485700</v>
       </c>
       <c r="H100" s="3">
-        <v>-182300</v>
+        <v>-187300</v>
       </c>
       <c r="I100" s="3">
-        <v>-388100</v>
+        <v>-398800</v>
       </c>
       <c r="J100" s="3">
-        <v>-995400</v>
+        <v>-1022600</v>
       </c>
       <c r="K100" s="3">
         <v>-716900</v>
@@ -4464,13 +4464,13 @@
         <v>-1500</v>
       </c>
       <c r="H101" s="3">
-        <v>-4000</v>
+        <v>-4100</v>
       </c>
       <c r="I101" s="3">
         <v>400</v>
       </c>
       <c r="J101" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="K101" s="3">
         <v>-1300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>314300</v>
+        <v>322900</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F102" s="3">
-        <v>281000</v>
+        <v>288700</v>
       </c>
       <c r="G102" s="3">
-        <v>240000</v>
+        <v>246500</v>
       </c>
       <c r="H102" s="3">
-        <v>-290200</v>
+        <v>-298100</v>
       </c>
       <c r="I102" s="3">
-        <v>565900</v>
+        <v>581400</v>
       </c>
       <c r="J102" s="3">
-        <v>-709700</v>
+        <v>-729100</v>
       </c>
       <c r="K102" s="3">
         <v>259000</v>

--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>KT</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19782200</v>
+        <v>20271400</v>
       </c>
       <c r="E8" s="3">
-        <v>19237500</v>
+        <v>20387000</v>
       </c>
       <c r="F8" s="3">
-        <v>18673500</v>
+        <v>20902300</v>
       </c>
       <c r="G8" s="3">
-        <v>17937500</v>
+        <v>22144700</v>
       </c>
       <c r="H8" s="3">
-        <v>18256500</v>
+        <v>21084700</v>
       </c>
       <c r="I8" s="3">
-        <v>17595100</v>
+        <v>21051900</v>
       </c>
       <c r="J8" s="3">
-        <v>17540500</v>
+        <v>22042300</v>
       </c>
       <c r="K8" s="3">
         <v>17285200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7046900</v>
+        <v>18778100</v>
       </c>
       <c r="E9" s="3">
-        <v>7191600</v>
+        <v>18754400</v>
       </c>
       <c r="F9" s="3">
-        <v>7413200</v>
+        <v>19256100</v>
       </c>
       <c r="G9" s="3">
-        <v>7242000</v>
+        <v>13114900</v>
       </c>
       <c r="H9" s="3">
-        <v>7641100</v>
+        <v>12689900</v>
       </c>
       <c r="I9" s="3">
-        <v>7080900</v>
+        <v>12354900</v>
       </c>
       <c r="J9" s="3">
-        <v>6933200</v>
+        <v>12434000</v>
       </c>
       <c r="K9" s="3">
         <v>6724800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12735300</v>
+        <v>1493300</v>
       </c>
       <c r="E10" s="3">
-        <v>12045900</v>
+        <v>1632600</v>
       </c>
       <c r="F10" s="3">
-        <v>11260300</v>
+        <v>1646200</v>
       </c>
       <c r="G10" s="3">
-        <v>10695500</v>
+        <v>9029700</v>
       </c>
       <c r="H10" s="3">
-        <v>10615500</v>
+        <v>8394800</v>
       </c>
       <c r="I10" s="3">
-        <v>10514200</v>
+        <v>8697000</v>
       </c>
       <c r="J10" s="3">
-        <v>10607300</v>
+        <v>9608300</v>
       </c>
       <c r="K10" s="3">
         <v>10560400</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>74800</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3">
-        <v>131200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>126700</v>
-      </c>
       <c r="G12" s="3">
-        <v>117700</v>
+        <v>144200</v>
       </c>
       <c r="H12" s="3">
-        <v>123800</v>
+        <v>142900</v>
       </c>
       <c r="I12" s="3">
-        <v>132600</v>
+        <v>158800</v>
       </c>
       <c r="J12" s="3">
-        <v>126500</v>
+        <v>157900</v>
       </c>
       <c r="K12" s="3">
         <v>127600</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>41700</v>
+        <v>139200</v>
       </c>
       <c r="E14" s="3">
-        <v>-275600</v>
+        <v>-210200</v>
       </c>
       <c r="F14" s="3">
-        <v>-97200</v>
+        <v>-44700</v>
       </c>
       <c r="G14" s="3">
-        <v>92400</v>
+        <v>321000</v>
       </c>
       <c r="H14" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-57000</v>
+        <v>139200</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="J14" s="3">
-        <v>-5700</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>40300</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2857600</v>
+        <v>2583200</v>
       </c>
       <c r="E15" s="3">
-        <v>2741900</v>
+        <v>2517700</v>
       </c>
       <c r="F15" s="3">
-        <v>2705700</v>
+        <v>2727300</v>
       </c>
       <c r="G15" s="3">
-        <v>2725700</v>
+        <v>3339500</v>
       </c>
       <c r="H15" s="3">
-        <v>2722100</v>
+        <v>3143800</v>
       </c>
       <c r="I15" s="3">
-        <v>2461300</v>
+        <v>2947900</v>
       </c>
       <c r="J15" s="3">
-        <v>2523400</v>
+        <v>3149500</v>
       </c>
       <c r="K15" s="3">
         <v>2542400</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>18586500</v>
+        <v>19187800</v>
       </c>
       <c r="E17" s="3">
-        <v>17694400</v>
+        <v>19222600</v>
       </c>
       <c r="F17" s="3">
-        <v>17322400</v>
+        <v>19692200</v>
       </c>
       <c r="G17" s="3">
-        <v>17141900</v>
+        <v>21122000</v>
       </c>
       <c r="H17" s="3">
-        <v>17383100</v>
+        <v>20080300</v>
       </c>
       <c r="I17" s="3">
-        <v>16592000</v>
+        <v>20063000</v>
       </c>
       <c r="J17" s="3">
-        <v>16503300</v>
+        <v>21041500</v>
       </c>
       <c r="K17" s="3">
         <v>16231100</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1195700</v>
+        <v>1083600</v>
       </c>
       <c r="E18" s="3">
-        <v>1543100</v>
+        <v>1164400</v>
       </c>
       <c r="F18" s="3">
-        <v>1351100</v>
+        <v>1210100</v>
       </c>
       <c r="G18" s="3">
-        <v>795600</v>
+        <v>1022700</v>
       </c>
       <c r="H18" s="3">
-        <v>873500</v>
+        <v>1004400</v>
       </c>
       <c r="I18" s="3">
-        <v>1003100</v>
+        <v>988900</v>
       </c>
       <c r="J18" s="3">
-        <v>1037100</v>
+        <v>1000800</v>
       </c>
       <c r="K18" s="3">
         <v>1054100</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>64700</v>
+        <v>-119300</v>
       </c>
       <c r="E20" s="3">
-        <v>97800</v>
+        <v>-146800</v>
       </c>
       <c r="F20" s="3">
-        <v>330300</v>
+        <v>-397600</v>
       </c>
       <c r="G20" s="3">
-        <v>133300</v>
+        <v>-239800</v>
       </c>
       <c r="H20" s="3">
-        <v>67500</v>
+        <v>23300</v>
       </c>
       <c r="I20" s="3">
-        <v>37600</v>
+        <v>13500</v>
       </c>
       <c r="J20" s="3">
-        <v>-182500</v>
+        <v>39900</v>
       </c>
       <c r="K20" s="3">
         <v>58800</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>4161200</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>24</v>
+        <v>3786100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3828900</v>
       </c>
       <c r="F21" s="3">
-        <v>4416900</v>
+        <v>4335000</v>
       </c>
       <c r="G21" s="3">
-        <v>3679700</v>
+        <v>4602000</v>
       </c>
       <c r="H21" s="3">
-        <v>3701400</v>
+        <v>4124900</v>
       </c>
       <c r="I21" s="3">
-        <v>3564400</v>
+        <v>3923300</v>
       </c>
       <c r="J21" s="3">
-        <v>3432900</v>
+        <v>4110400</v>
       </c>
       <c r="K21" s="3">
         <v>3713200</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>267300</v>
+        <v>274800</v>
       </c>
       <c r="E22" s="3">
-        <v>220400</v>
+        <v>233700</v>
       </c>
       <c r="F22" s="3">
-        <v>197500</v>
+        <v>221100</v>
       </c>
       <c r="G22" s="3">
-        <v>197700</v>
+        <v>242200</v>
       </c>
       <c r="H22" s="3">
-        <v>208800</v>
+        <v>241200</v>
       </c>
       <c r="I22" s="3">
-        <v>222700</v>
+        <v>266500</v>
       </c>
       <c r="J22" s="3">
-        <v>226800</v>
+        <v>283200</v>
       </c>
       <c r="K22" s="3">
         <v>256300</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>993100</v>
+        <v>1004500</v>
       </c>
       <c r="E23" s="3">
-        <v>1420600</v>
+        <v>1504000</v>
       </c>
       <c r="F23" s="3">
-        <v>1483800</v>
+        <v>1660900</v>
       </c>
       <c r="G23" s="3">
-        <v>731300</v>
+        <v>947900</v>
       </c>
       <c r="H23" s="3">
-        <v>732200</v>
+        <v>845600</v>
       </c>
       <c r="I23" s="3">
-        <v>818100</v>
+        <v>928800</v>
       </c>
       <c r="J23" s="3">
-        <v>627800</v>
+        <v>764800</v>
       </c>
       <c r="K23" s="3">
         <v>856500</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>251500</v>
+        <v>254800</v>
       </c>
       <c r="E24" s="3">
-        <v>379800</v>
+        <v>402200</v>
       </c>
       <c r="F24" s="3">
-        <v>389300</v>
+        <v>435700</v>
       </c>
       <c r="G24" s="3">
-        <v>203700</v>
+        <v>262200</v>
       </c>
       <c r="H24" s="3">
-        <v>232700</v>
+        <v>268800</v>
       </c>
       <c r="I24" s="3">
-        <v>246300</v>
+        <v>282600</v>
       </c>
       <c r="J24" s="3">
-        <v>206600</v>
+        <v>253400</v>
       </c>
       <c r="K24" s="3">
         <v>250200</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>741500</v>
+        <v>749700</v>
       </c>
       <c r="E26" s="3">
-        <v>1040700</v>
+        <v>1101800</v>
       </c>
       <c r="F26" s="3">
-        <v>1094500</v>
+        <v>1225200</v>
       </c>
       <c r="G26" s="3">
-        <v>527500</v>
+        <v>685700</v>
       </c>
       <c r="H26" s="3">
-        <v>499500</v>
+        <v>576800</v>
       </c>
       <c r="I26" s="3">
-        <v>571700</v>
+        <v>646200</v>
       </c>
       <c r="J26" s="3">
-        <v>421100</v>
+        <v>511400</v>
       </c>
       <c r="K26" s="3">
         <v>606400</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>756500</v>
+        <v>766000</v>
       </c>
       <c r="E27" s="3">
-        <v>946900</v>
+        <v>1001600</v>
       </c>
       <c r="F27" s="3">
-        <v>1015900</v>
+        <v>1137200</v>
       </c>
       <c r="G27" s="3">
-        <v>493500</v>
+        <v>644000</v>
       </c>
       <c r="H27" s="3">
-        <v>461800</v>
+        <v>533400</v>
       </c>
       <c r="I27" s="3">
-        <v>516300</v>
+        <v>579900</v>
       </c>
       <c r="J27" s="3">
-        <v>357600</v>
+        <v>432100</v>
       </c>
       <c r="K27" s="3">
         <v>606400</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>-65900</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-64700</v>
+        <v>119300</v>
       </c>
       <c r="E32" s="3">
-        <v>-97800</v>
+        <v>146800</v>
       </c>
       <c r="F32" s="3">
-        <v>-330300</v>
+        <v>397600</v>
       </c>
       <c r="G32" s="3">
-        <v>-133300</v>
+        <v>239800</v>
       </c>
       <c r="H32" s="3">
-        <v>-67500</v>
+        <v>-23300</v>
       </c>
       <c r="I32" s="3">
-        <v>-37600</v>
+        <v>-13500</v>
       </c>
       <c r="J32" s="3">
-        <v>182500</v>
+        <v>-39900</v>
       </c>
       <c r="K32" s="3">
         <v>-58800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>756500</v>
+        <v>766000</v>
       </c>
       <c r="E33" s="3">
-        <v>946900</v>
+        <v>1002300</v>
       </c>
       <c r="F33" s="3">
-        <v>1015900</v>
+        <v>1139100</v>
       </c>
       <c r="G33" s="3">
-        <v>493500</v>
+        <v>644000</v>
       </c>
       <c r="H33" s="3">
-        <v>461800</v>
+        <v>533400</v>
       </c>
       <c r="I33" s="3">
-        <v>516300</v>
+        <v>579900</v>
       </c>
       <c r="J33" s="3">
-        <v>357600</v>
+        <v>432100</v>
       </c>
       <c r="K33" s="3">
         <v>540400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>756500</v>
+        <v>766000</v>
       </c>
       <c r="E35" s="3">
-        <v>946900</v>
+        <v>1002300</v>
       </c>
       <c r="F35" s="3">
-        <v>1015900</v>
+        <v>1139100</v>
       </c>
       <c r="G35" s="3">
-        <v>493500</v>
+        <v>644000</v>
       </c>
       <c r="H35" s="3">
-        <v>461800</v>
+        <v>533400</v>
       </c>
       <c r="I35" s="3">
-        <v>516300</v>
+        <v>579900</v>
       </c>
       <c r="J35" s="3">
-        <v>357600</v>
+        <v>432100</v>
       </c>
       <c r="K35" s="3">
         <v>540400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2122500</v>
+        <v>2220600</v>
       </c>
       <c r="E41" s="3">
-        <v>1836800</v>
+        <v>1947400</v>
       </c>
       <c r="F41" s="3">
-        <v>2264700</v>
+        <v>2535000</v>
       </c>
       <c r="G41" s="3">
-        <v>1976000</v>
+        <v>2420900</v>
       </c>
       <c r="H41" s="3">
-        <v>1729400</v>
+        <v>1997300</v>
       </c>
       <c r="I41" s="3">
-        <v>2027600</v>
+        <v>2428400</v>
       </c>
       <c r="J41" s="3">
-        <v>1446100</v>
+        <v>1805000</v>
       </c>
       <c r="K41" s="3">
         <v>2204200</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1080200</v>
+        <v>1071000</v>
       </c>
       <c r="E42" s="3">
-        <v>991800</v>
+        <v>1016800</v>
       </c>
       <c r="F42" s="3">
-        <v>889200</v>
+        <v>968900</v>
       </c>
       <c r="G42" s="3">
-        <v>902100</v>
+        <v>1100200</v>
       </c>
       <c r="H42" s="3">
-        <v>651300</v>
+        <v>726000</v>
       </c>
       <c r="I42" s="3">
-        <v>746100</v>
+        <v>871000</v>
       </c>
       <c r="J42" s="3">
-        <v>729500</v>
+        <v>907900</v>
       </c>
       <c r="K42" s="3">
         <v>547600</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5380200</v>
+        <v>5531900</v>
       </c>
       <c r="E43" s="3">
-        <v>4574700</v>
+        <v>4850200</v>
       </c>
       <c r="F43" s="3">
-        <v>3820100</v>
+        <v>4276000</v>
       </c>
       <c r="G43" s="3">
-        <v>3678400</v>
+        <v>4506700</v>
       </c>
       <c r="H43" s="3">
-        <v>4480900</v>
+        <v>5175100</v>
       </c>
       <c r="I43" s="3">
-        <v>4358600</v>
+        <v>5106100</v>
       </c>
       <c r="J43" s="3">
-        <v>4501300</v>
+        <v>5591900</v>
       </c>
       <c r="K43" s="3">
         <v>4053300</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>684200</v>
+        <v>762200</v>
       </c>
       <c r="E44" s="3">
-        <v>531900</v>
+        <v>570700</v>
       </c>
       <c r="F44" s="3">
-        <v>385600</v>
+        <v>431600</v>
       </c>
       <c r="G44" s="3">
-        <v>401000</v>
+        <v>491300</v>
       </c>
       <c r="H44" s="3">
-        <v>499100</v>
+        <v>576400</v>
       </c>
       <c r="I44" s="3">
-        <v>513000</v>
+        <v>965300</v>
       </c>
       <c r="J44" s="3">
-        <v>343300</v>
+        <v>601000</v>
       </c>
       <c r="K44" s="3">
         <v>287300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1621600</v>
+        <v>1668700</v>
       </c>
       <c r="E45" s="3">
-        <v>1575900</v>
+        <v>1705500</v>
       </c>
       <c r="F45" s="3">
-        <v>1534100</v>
+        <v>1743700</v>
       </c>
       <c r="G45" s="3">
-        <v>1408200</v>
+        <v>1730400</v>
       </c>
       <c r="H45" s="3">
-        <v>1562200</v>
+        <v>1830400</v>
       </c>
       <c r="I45" s="3">
-        <v>1275400</v>
+        <v>1550100</v>
       </c>
       <c r="J45" s="3">
-        <v>234100</v>
+        <v>294700</v>
       </c>
       <c r="K45" s="3">
         <v>236500</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10888600</v>
+        <v>11254400</v>
       </c>
       <c r="E46" s="3">
-        <v>9511100</v>
+        <v>10090600</v>
       </c>
       <c r="F46" s="3">
-        <v>8893800</v>
+        <v>9955300</v>
       </c>
       <c r="G46" s="3">
-        <v>8365600</v>
+        <v>10249500</v>
       </c>
       <c r="H46" s="3">
-        <v>8922900</v>
+        <v>10305200</v>
       </c>
       <c r="I46" s="3">
-        <v>8920700</v>
+        <v>10921000</v>
       </c>
       <c r="J46" s="3">
-        <v>7254300</v>
+        <v>9200500</v>
       </c>
       <c r="K46" s="3">
         <v>7328900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4264400</v>
+        <v>3218700</v>
       </c>
       <c r="E47" s="3">
-        <v>4104900</v>
+        <v>3049500</v>
       </c>
       <c r="F47" s="3">
-        <v>2401600</v>
+        <v>1715100</v>
       </c>
       <c r="G47" s="3">
-        <v>1764700</v>
+        <v>1010900</v>
       </c>
       <c r="H47" s="3">
-        <v>1703300</v>
+        <v>919000</v>
       </c>
       <c r="I47" s="3">
-        <v>1303900</v>
+        <v>800200</v>
       </c>
       <c r="J47" s="3">
-        <v>1397400</v>
+        <v>963900</v>
       </c>
       <c r="K47" s="3">
         <v>1259900</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13781400</v>
+        <v>12475000</v>
       </c>
       <c r="E48" s="3">
-        <v>13489400</v>
+        <v>12764300</v>
       </c>
       <c r="F48" s="3">
-        <v>13075400</v>
+        <v>13191500</v>
       </c>
       <c r="G48" s="3">
-        <v>12593800</v>
+        <v>14172300</v>
       </c>
       <c r="H48" s="3">
-        <v>12330800</v>
+        <v>13039200</v>
       </c>
       <c r="I48" s="3">
-        <v>10619500</v>
+        <v>11738800</v>
       </c>
       <c r="J48" s="3">
-        <v>11063900</v>
+        <v>12695700</v>
       </c>
       <c r="K48" s="3">
         <v>11749700</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900400</v>
+        <v>1847100</v>
       </c>
       <c r="E49" s="3">
-        <v>2347400</v>
+        <v>2352100</v>
       </c>
       <c r="F49" s="3">
-        <v>2585500</v>
+        <v>2702400</v>
       </c>
       <c r="G49" s="3">
-        <v>1620900</v>
+        <v>1727800</v>
       </c>
       <c r="H49" s="3">
-        <v>2125500</v>
+        <v>2218600</v>
       </c>
       <c r="I49" s="3">
-        <v>2555300</v>
+        <v>2759500</v>
       </c>
       <c r="J49" s="3">
-        <v>1974500</v>
+        <v>2072700</v>
       </c>
       <c r="K49" s="3">
         <v>2297300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1197700</v>
+        <v>3393400</v>
       </c>
       <c r="E52" s="3">
-        <v>1282600</v>
+        <v>3425500</v>
       </c>
       <c r="F52" s="3">
-        <v>913300</v>
+        <v>2586900</v>
       </c>
       <c r="G52" s="3">
-        <v>901800</v>
+        <v>2330300</v>
       </c>
       <c r="H52" s="3">
-        <v>822500</v>
+        <v>2127200</v>
       </c>
       <c r="I52" s="3">
-        <v>742200</v>
+        <v>1889100</v>
       </c>
       <c r="J52" s="3">
-        <v>608000</v>
+        <v>1663900</v>
       </c>
       <c r="K52" s="3">
         <v>610800</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>32032500</v>
+        <v>32998900</v>
       </c>
       <c r="E54" s="3">
-        <v>30735500</v>
+        <v>32593400</v>
       </c>
       <c r="F54" s="3">
-        <v>27869500</v>
+        <v>31195900</v>
       </c>
       <c r="G54" s="3">
-        <v>25246900</v>
+        <v>30932200</v>
       </c>
       <c r="H54" s="3">
-        <v>25905100</v>
+        <v>29918100</v>
       </c>
       <c r="I54" s="3">
-        <v>24141600</v>
+        <v>29170600</v>
       </c>
       <c r="J54" s="3">
-        <v>22298200</v>
+        <v>27985400</v>
       </c>
       <c r="K54" s="3">
         <v>23246700</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>973300</v>
+        <v>1000800</v>
       </c>
       <c r="E57" s="3">
-        <v>862900</v>
+        <v>914800</v>
       </c>
       <c r="F57" s="3">
-        <v>1152900</v>
+        <v>1290500</v>
       </c>
       <c r="G57" s="3">
-        <v>929800</v>
+        <v>1139200</v>
       </c>
       <c r="H57" s="3">
-        <v>978600</v>
+        <v>1130200</v>
       </c>
       <c r="I57" s="3">
-        <v>927400</v>
+        <v>1110700</v>
       </c>
       <c r="J57" s="3">
-        <v>1049500</v>
+        <v>1309900</v>
       </c>
       <c r="K57" s="3">
         <v>939300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2524800</v>
+        <v>2596700</v>
       </c>
       <c r="E58" s="3">
-        <v>1607200</v>
+        <v>1704000</v>
       </c>
       <c r="F58" s="3">
-        <v>1548100</v>
+        <v>1747900</v>
       </c>
       <c r="G58" s="3">
-        <v>1322500</v>
+        <v>1620300</v>
       </c>
       <c r="H58" s="3">
-        <v>1183600</v>
+        <v>1367800</v>
       </c>
       <c r="I58" s="3">
-        <v>1026400</v>
+        <v>1548900</v>
       </c>
       <c r="J58" s="3">
-        <v>1180100</v>
+        <v>1472900</v>
       </c>
       <c r="K58" s="3">
         <v>1383200</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6362400</v>
+        <v>6618500</v>
       </c>
       <c r="E59" s="3">
-        <v>5554400</v>
+        <v>5888800</v>
       </c>
       <c r="F59" s="3">
-        <v>4853400</v>
+        <v>5417600</v>
       </c>
       <c r="G59" s="3">
-        <v>4642100</v>
+        <v>5687400</v>
       </c>
       <c r="H59" s="3">
-        <v>6222800</v>
+        <v>6292100</v>
       </c>
       <c r="I59" s="3">
-        <v>5087100</v>
+        <v>5778900</v>
       </c>
       <c r="J59" s="3">
-        <v>4876100</v>
+        <v>6086000</v>
       </c>
       <c r="K59" s="3">
         <v>4871700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9860600</v>
+        <v>10216000</v>
       </c>
       <c r="E60" s="3">
-        <v>8024500</v>
+        <v>8507600</v>
       </c>
       <c r="F60" s="3">
-        <v>7554300</v>
+        <v>8456000</v>
       </c>
       <c r="G60" s="3">
-        <v>6894400</v>
+        <v>8446900</v>
       </c>
       <c r="H60" s="3">
-        <v>7611000</v>
+        <v>8790100</v>
       </c>
       <c r="I60" s="3">
-        <v>7040800</v>
+        <v>8438500</v>
       </c>
       <c r="J60" s="3">
-        <v>7105600</v>
+        <v>8868800</v>
       </c>
       <c r="K60" s="3">
         <v>7194300</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6023700</v>
+        <v>6211900</v>
       </c>
       <c r="E61" s="3">
-        <v>6776800</v>
+        <v>7211600</v>
       </c>
       <c r="F61" s="3">
-        <v>5649700</v>
+        <v>6324200</v>
       </c>
       <c r="G61" s="3">
-        <v>5022400</v>
+        <v>6153400</v>
       </c>
       <c r="H61" s="3">
-        <v>5199000</v>
+        <v>6021000</v>
       </c>
       <c r="I61" s="3">
-        <v>3959900</v>
+        <v>5078000</v>
       </c>
       <c r="J61" s="3">
-        <v>3832600</v>
+        <v>4783700</v>
       </c>
       <c r="K61" s="3">
         <v>4788600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2227300</v>
+        <v>1337600</v>
       </c>
       <c r="E62" s="3">
-        <v>2123200</v>
+        <v>1291300</v>
       </c>
       <c r="F62" s="3">
-        <v>2240100</v>
+        <v>1637400</v>
       </c>
       <c r="G62" s="3">
-        <v>1666500</v>
+        <v>1162900</v>
       </c>
       <c r="H62" s="3">
-        <v>2044500</v>
+        <v>1184000</v>
       </c>
       <c r="I62" s="3">
-        <v>2092500</v>
+        <v>1699200</v>
       </c>
       <c r="J62" s="3">
-        <v>1452000</v>
+        <v>1416100</v>
       </c>
       <c r="K62" s="3">
         <v>1539800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>19470600</v>
+        <v>18699700</v>
       </c>
       <c r="E66" s="3">
-        <v>18276400</v>
+        <v>17952400</v>
       </c>
       <c r="F66" s="3">
-        <v>16637100</v>
+        <v>17287500</v>
       </c>
       <c r="G66" s="3">
-        <v>14738300</v>
+        <v>16642100</v>
       </c>
       <c r="H66" s="3">
-        <v>15657500</v>
+        <v>16766300</v>
       </c>
       <c r="I66" s="3">
-        <v>14239600</v>
+        <v>16003300</v>
       </c>
       <c r="J66" s="3">
-        <v>13434100</v>
+        <v>15644500</v>
       </c>
       <c r="K66" s="3">
         <v>14550800</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10870800</v>
+        <v>11163100</v>
       </c>
       <c r="E72" s="3">
-        <v>10693000</v>
+        <v>11335200</v>
       </c>
       <c r="F72" s="3">
-        <v>9965500</v>
+        <v>11155000</v>
       </c>
       <c r="G72" s="3">
-        <v>9116600</v>
+        <v>11169500</v>
       </c>
       <c r="H72" s="3">
-        <v>8725300</v>
+        <v>10077000</v>
       </c>
       <c r="I72" s="3">
-        <v>8496600</v>
+        <v>10111000</v>
       </c>
       <c r="J72" s="3">
-        <v>7491300</v>
+        <v>9324600</v>
       </c>
       <c r="K72" s="3">
         <v>7339000</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12561900</v>
+        <v>12901900</v>
       </c>
       <c r="E76" s="3">
-        <v>12459100</v>
+        <v>13207700</v>
       </c>
       <c r="F76" s="3">
-        <v>11232400</v>
+        <v>12573100</v>
       </c>
       <c r="G76" s="3">
-        <v>10508600</v>
+        <v>12875000</v>
       </c>
       <c r="H76" s="3">
-        <v>10247500</v>
+        <v>11835000</v>
       </c>
       <c r="I76" s="3">
-        <v>9902000</v>
+        <v>11794200</v>
       </c>
       <c r="J76" s="3">
-        <v>8864100</v>
+        <v>11038100</v>
       </c>
       <c r="K76" s="3">
         <v>8695900</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>756500</v>
+        <v>766000</v>
       </c>
       <c r="E81" s="3">
-        <v>946900</v>
+        <v>1002300</v>
       </c>
       <c r="F81" s="3">
-        <v>1015900</v>
+        <v>1139100</v>
       </c>
       <c r="G81" s="3">
-        <v>493500</v>
+        <v>644000</v>
       </c>
       <c r="H81" s="3">
-        <v>461800</v>
+        <v>533400</v>
       </c>
       <c r="I81" s="3">
-        <v>516300</v>
+        <v>579900</v>
       </c>
       <c r="J81" s="3">
-        <v>357600</v>
+        <v>432100</v>
       </c>
       <c r="K81" s="3">
         <v>540400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2900800</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>24</v>
+        <v>2449100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2451800</v>
       </c>
       <c r="F83" s="3">
-        <v>2735500</v>
+        <v>2554300</v>
       </c>
       <c r="G83" s="3">
-        <v>2750700</v>
+        <v>2792900</v>
       </c>
       <c r="H83" s="3">
-        <v>2760400</v>
+        <v>2599400</v>
       </c>
       <c r="I83" s="3">
-        <v>2523700</v>
+        <v>2457100</v>
       </c>
       <c r="J83" s="3">
-        <v>2578300</v>
+        <v>2623500</v>
       </c>
       <c r="K83" s="3">
         <v>2600300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4127500</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>24</v>
+        <v>4243900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2860200</v>
       </c>
       <c r="F89" s="3">
-        <v>4171400</v>
+        <v>4669300</v>
       </c>
       <c r="G89" s="3">
-        <v>3554900</v>
+        <v>4355400</v>
       </c>
       <c r="H89" s="3">
-        <v>2808900</v>
+        <v>3244000</v>
       </c>
       <c r="I89" s="3">
-        <v>3007800</v>
+        <v>3602500</v>
       </c>
       <c r="J89" s="3">
-        <v>2908300</v>
+        <v>3630000</v>
       </c>
       <c r="K89" s="3">
         <v>3625800</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2770500</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>24</v>
+        <v>-2847800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2735200</v>
       </c>
       <c r="F91" s="3">
-        <v>-2624500</v>
+        <v>-2934100</v>
       </c>
       <c r="G91" s="3">
-        <v>-2410000</v>
+        <v>-2947400</v>
       </c>
       <c r="H91" s="3">
-        <v>-2452200</v>
+        <v>-2826600</v>
       </c>
       <c r="I91" s="3">
-        <v>-1695700</v>
+        <v>-2030900</v>
       </c>
       <c r="J91" s="3">
-        <v>-1831700</v>
+        <v>-2286200</v>
       </c>
       <c r="K91" s="3">
         <v>-2100900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3465400</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>24</v>
+        <v>-3563100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3847500</v>
       </c>
       <c r="F94" s="3">
-        <v>-3853100</v>
+        <v>-4313000</v>
       </c>
       <c r="G94" s="3">
-        <v>-2821100</v>
+        <v>-3456400</v>
       </c>
       <c r="H94" s="3">
-        <v>-2915600</v>
+        <v>-3367300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2028100</v>
+        <v>-2429000</v>
       </c>
       <c r="J94" s="3">
-        <v>-2612400</v>
+        <v>-3260700</v>
       </c>
       <c r="K94" s="3">
         <v>-2648600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-395100</v>
+        <v>406300</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>358100</v>
       </c>
       <c r="F96" s="3">
-        <v>-262800</v>
+        <v>294100</v>
       </c>
       <c r="G96" s="3">
-        <v>-232900</v>
+        <v>247900</v>
       </c>
       <c r="H96" s="3">
-        <v>-228900</v>
+        <v>233600</v>
       </c>
       <c r="I96" s="3">
-        <v>-224000</v>
+        <v>220200</v>
       </c>
       <c r="J96" s="3">
-        <v>-182400</v>
+        <v>183500</v>
       </c>
       <c r="K96" s="3">
         <v>-139900</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-339600</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>24</v>
+        <v>-349200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>532200</v>
       </c>
       <c r="F100" s="3">
-        <v>-31000</v>
+        <v>-34700</v>
       </c>
       <c r="G100" s="3">
-        <v>-485700</v>
+        <v>-595100</v>
       </c>
       <c r="H100" s="3">
-        <v>-187300</v>
+        <v>-216300</v>
       </c>
       <c r="I100" s="3">
-        <v>-398800</v>
+        <v>-477600</v>
       </c>
       <c r="J100" s="3">
-        <v>-1022600</v>
+        <v>-1276400</v>
       </c>
       <c r="K100" s="3">
         <v>-716900</v>
@@ -4454,23 +4454,23 @@
       <c r="D101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>24</v>
+      <c r="E101" s="3">
+        <v>1400</v>
       </c>
       <c r="F101" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="G101" s="3">
-        <v>-1500</v>
+        <v>-1900</v>
       </c>
       <c r="H101" s="3">
-        <v>-4100</v>
+        <v>-4700</v>
       </c>
       <c r="I101" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J101" s="3">
-        <v>-2400</v>
+        <v>-2900</v>
       </c>
       <c r="K101" s="3">
         <v>-1300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>322900</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>24</v>
+        <v>332000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-453700</v>
       </c>
       <c r="F102" s="3">
-        <v>288700</v>
+        <v>323200</v>
       </c>
       <c r="G102" s="3">
-        <v>246500</v>
+        <v>302100</v>
       </c>
       <c r="H102" s="3">
-        <v>-298100</v>
+        <v>-344300</v>
       </c>
       <c r="I102" s="3">
-        <v>581400</v>
+        <v>696400</v>
       </c>
       <c r="J102" s="3">
-        <v>-729100</v>
+        <v>-910000</v>
       </c>
       <c r="K102" s="3">
         <v>259000</v>

--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>20271400</v>
+        <v>17892200</v>
       </c>
       <c r="E8" s="3">
+        <v>20340100</v>
+      </c>
+      <c r="F8" s="3">
         <v>20387000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20902300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22144700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21084700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21051900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22042300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17285200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16488100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18741800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21892700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20700800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19879000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>18778100</v>
+        <v>11697700</v>
       </c>
       <c r="E9" s="3">
-        <v>18754400</v>
+        <v>12731000</v>
       </c>
       <c r="F9" s="3">
-        <v>19256100</v>
+        <v>12865800</v>
       </c>
       <c r="G9" s="3">
+        <v>13275600</v>
+      </c>
+      <c r="H9" s="3">
         <v>13114900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12689900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12354900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12434000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6724800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6518700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7504500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6253800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5936900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6602100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1493300</v>
+        <v>6194400</v>
       </c>
       <c r="E10" s="3">
-        <v>1632600</v>
+        <v>7609100</v>
       </c>
       <c r="F10" s="3">
-        <v>1646200</v>
+        <v>7521200</v>
       </c>
       <c r="G10" s="3">
+        <v>7626700</v>
+      </c>
+      <c r="H10" s="3">
         <v>9029700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8394800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8697000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9608300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10560400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9969400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11237300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15638900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14763900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13277000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E12" s="3">
         <v>48700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>74800</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>144200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>142900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>158800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>157900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>127600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>136000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>161300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>156000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>257300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>277000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>158700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>201000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-275000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-116200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>321000</v>
+      </c>
+      <c r="I14" s="3">
         <v>139200</v>
       </c>
-      <c r="E14" s="3">
-        <v>-210200</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-44700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>321000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>139200</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>40300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>115900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>89900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>39300</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2583200</v>
+        <v>2625000</v>
       </c>
       <c r="E15" s="3">
-        <v>2517700</v>
+        <v>2938200</v>
       </c>
       <c r="F15" s="3">
-        <v>2727300</v>
+        <v>2907000</v>
       </c>
       <c r="G15" s="3">
+        <v>3028700</v>
+      </c>
+      <c r="H15" s="3">
         <v>3339500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3143800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2947900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3149500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2542400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2470600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2793600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3245200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2750200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2661700</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>19187800</v>
+        <v>17344200</v>
       </c>
       <c r="E17" s="3">
-        <v>19222600</v>
+        <v>19067900</v>
       </c>
       <c r="F17" s="3">
-        <v>19692200</v>
+        <v>19274900</v>
       </c>
       <c r="G17" s="3">
+        <v>19754500</v>
+      </c>
+      <c r="H17" s="3">
         <v>21122000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20080300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20063000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21041500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16231100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15647200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19173300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21603000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19292300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18090700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1083600</v>
+        <v>548000</v>
       </c>
       <c r="E18" s="3">
-        <v>1164400</v>
+        <v>1272200</v>
       </c>
       <c r="F18" s="3">
-        <v>1210100</v>
+        <v>1112100</v>
       </c>
       <c r="G18" s="3">
+        <v>1147800</v>
+      </c>
+      <c r="H18" s="3">
         <v>1022700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1004400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>988900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1000800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1054100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>840900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-431500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>289700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1408400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1788400</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-119300</v>
+        <v>-8000</v>
       </c>
       <c r="E20" s="3">
-        <v>-146800</v>
+        <v>35700</v>
       </c>
       <c r="F20" s="3">
-        <v>-397600</v>
+        <v>-134300</v>
       </c>
       <c r="G20" s="3">
+        <v>-388400</v>
+      </c>
+      <c r="H20" s="3">
         <v>-239800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>23300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>39900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>58800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-22900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-285500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>85400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>177300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>92500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3786100</v>
+        <v>3180900</v>
       </c>
       <c r="E21" s="3">
-        <v>3828900</v>
+        <v>4174800</v>
       </c>
       <c r="F21" s="3">
-        <v>4335000</v>
+        <v>4153400</v>
       </c>
       <c r="G21" s="3">
+        <v>4564900</v>
+      </c>
+      <c r="H21" s="3">
         <v>4602000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4124900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3923300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4110400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3713200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3475200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2521100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3633700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4402500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4547700</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>253600</v>
+      </c>
+      <c r="E22" s="3">
         <v>274800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>233700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>221100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>242200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>241200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>266500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>283200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>256300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>285600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>399100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>409800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>397300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>432500</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1004500</v>
+        <v>395800</v>
       </c>
       <c r="E23" s="3">
+        <v>1021100</v>
+      </c>
+      <c r="F23" s="3">
         <v>1504000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1660900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>947900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>845600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>928800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>764800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>856500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>532400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1116000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-34700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1188500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1448300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>254800</v>
+        <v>113500</v>
       </c>
       <c r="E24" s="3">
+        <v>258600</v>
+      </c>
+      <c r="F24" s="3">
         <v>402200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>435700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>262200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>268800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>282600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>253400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>250200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>169600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-231800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>45100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>233400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>286600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>749700</v>
+        <v>282300</v>
       </c>
       <c r="E26" s="3">
+        <v>762500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1101800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1225200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>685700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>576800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>646200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>511400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>606400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>362800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-884200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-79800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>955100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1161700</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>766000</v>
+        <v>317600</v>
       </c>
       <c r="E27" s="3">
+        <v>777900</v>
+      </c>
+      <c r="F27" s="3">
         <v>1001600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1137200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>644000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>533400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>579900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>432100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>606400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>303900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-939900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-172800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>905200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1152000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1611,26 +1671,29 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-65900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>105300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>53700</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-26500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>148400</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>119300</v>
+        <v>8000</v>
       </c>
       <c r="E32" s="3">
-        <v>146800</v>
+        <v>-35700</v>
       </c>
       <c r="F32" s="3">
-        <v>397600</v>
+        <v>134300</v>
       </c>
       <c r="G32" s="3">
+        <v>388400</v>
+      </c>
+      <c r="H32" s="3">
         <v>239800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-23300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-39900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-58800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>22900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>285500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-85400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-177300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-92500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>766000</v>
+        <v>318400</v>
       </c>
       <c r="E33" s="3">
+        <v>778800</v>
+      </c>
+      <c r="F33" s="3">
         <v>1002300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1139100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>644000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>533400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>579900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>432100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>540400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>409200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-886200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-172800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>878700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1300400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>766000</v>
+        <v>318400</v>
       </c>
       <c r="E35" s="3">
+        <v>778800</v>
+      </c>
+      <c r="F35" s="3">
         <v>1002300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1139100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>644000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>533400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>579900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>432100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>540400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>409200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-886200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-172800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>878700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1300400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2515900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2220600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1947400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2535000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2420900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1997300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2428400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1805000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2204200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1894000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1586500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1884500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2454100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>597300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>785600</v>
+      </c>
+      <c r="E42" s="3">
         <v>1071000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1016800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>968900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1100200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>726000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>871000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>907900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>547600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>216800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>279500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>436900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1708200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1515700</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4162200</v>
+      </c>
+      <c r="E43" s="3">
         <v>5531900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4850200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4276000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4506700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5175100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5106100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5591900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4053300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3617500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4858500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5831100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7453300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5811000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>762200</v>
+        <v>636500</v>
       </c>
       <c r="E44" s="3">
+        <v>703500</v>
+      </c>
+      <c r="F44" s="3">
         <v>570700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>431600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>491300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>576400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>965300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>601000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>287300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>388800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>351900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>613000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1346800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>607300</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1547400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1668700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1705500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1743700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1730400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1830400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1550100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>294700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>236500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>234500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>293700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>309000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>305200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>280300</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11254400</v>
+        <v>9647600</v>
       </c>
       <c r="E46" s="3">
+        <v>11195700</v>
+      </c>
+      <c r="F46" s="3">
         <v>10090600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9955300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10249500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10305200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10921000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9200500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7328900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6351600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7370000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9074400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8834600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8811600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2748100</v>
+      </c>
+      <c r="E47" s="3">
         <v>3218700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3049500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1715100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1010900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>919000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>800200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>963900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1259900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1208000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2354300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2525800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3649000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3468200</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10857100</v>
+      </c>
+      <c r="E48" s="3">
         <v>12475000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12764300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13191500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14172300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13039200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11738800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12695700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11749700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11529900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14723400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15918100</v>
       </c>
-      <c r="O48" s="3" t="s">
+      <c r="P48" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13663600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1190500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1847100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2352100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2702400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1727800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2218600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2759500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2072700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2297300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1923800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2977000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3482900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5398000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2379100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3216500</v>
+      </c>
+      <c r="E52" s="3">
         <v>3393400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3425500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2586900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2330300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2127200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1889100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1663900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>610800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>699100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>966700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>712300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>593000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>554300</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>32998900</v>
+        <v>28349900</v>
       </c>
       <c r="E54" s="3">
+        <v>32935900</v>
+      </c>
+      <c r="F54" s="3">
         <v>32593400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31195900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30932200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29918100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29170600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27985400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23246700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21712500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28391400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31713600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29028600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28876900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>701800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>914800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1290500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1139200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1130200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1110700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1309900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>939300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>954900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1008000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1562200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1531200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1471800</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2879700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2596700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1704000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1747900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1620300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1367800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1548900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1472900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1383200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1322600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2499700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2766600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2697300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1942700</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6618500</v>
+        <v>5810800</v>
       </c>
       <c r="E59" s="3">
+        <v>6541200</v>
+      </c>
+      <c r="F59" s="3">
         <v>5888800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5417600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5687400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6292100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5778900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6086000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4871700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4116100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4881500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5885200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5235600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4456100</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10216000</v>
+        <v>9392300</v>
       </c>
       <c r="E60" s="3">
+        <v>10138700</v>
+      </c>
+      <c r="F60" s="3">
         <v>8507600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8456000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8446900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8790100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8438500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8868800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7194300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6393500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8389200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10213900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9464100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7870600</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4959300</v>
+      </c>
+      <c r="E61" s="3">
         <v>6211900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7211600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6324200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6153400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6021000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5078000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4783700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4788600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5182800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8311500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7745800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6944000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8078500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1005300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1337600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1291300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1637400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1162900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1184000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1699200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1416100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1539800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1133700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1789200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2071800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1517400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1643700</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>18699700</v>
+        <v>16167500</v>
       </c>
       <c r="E66" s="3">
+        <v>18622400</v>
+      </c>
+      <c r="F66" s="3">
         <v>17952400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17287500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16642100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16766300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16003300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15644500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14550800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13687100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19707300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21041400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18688900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18343100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>11163100</v>
+        <v>9328000</v>
       </c>
       <c r="E72" s="3">
+        <v>11177400</v>
+      </c>
+      <c r="F72" s="3">
         <v>11335200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11155000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11169500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10077000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10111000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9324600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7339000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6703900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7197500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9117600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17885900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9197700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12901900</v>
+        <v>10973600</v>
       </c>
       <c r="E76" s="3">
+        <v>12916200</v>
+      </c>
+      <c r="F76" s="3">
         <v>13207700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12573100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12875000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11835000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11794200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11038100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8695900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8025400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8684100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10672200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10339700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10533800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>766000</v>
+        <v>318400</v>
       </c>
       <c r="E81" s="3">
+        <v>778800</v>
+      </c>
+      <c r="F81" s="3">
         <v>1002300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1139100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>644000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>533400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>579900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>432100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>540400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>409200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-886200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-172800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>878700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1300400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2218900</v>
+      </c>
+      <c r="E83" s="3">
         <v>2449100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2451800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2554300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2792900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2599400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2457100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2623500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2693600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3238000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3294900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2783600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2696800</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3429200</v>
+      </c>
+      <c r="E89" s="3">
         <v>4243900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2860200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4669300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4355400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3244000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3602500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3630000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3625800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3130200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1609800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3741100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4809400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1947600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1969500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2847800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2735200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2934100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2947400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2826600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2030900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2286200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2305600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2396400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2810200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3158600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3155000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1926200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3563100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3847500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4313000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3456400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3367300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2429000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3260700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2648600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1777400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2663600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3442200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3235000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2399100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>590500</v>
+      </c>
+      <c r="E96" s="3">
         <v>406300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>358100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>294100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>247900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>233600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>220200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>183500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-139900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-30800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-187100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-465300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-827100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1063400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-941000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-349200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>532200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-34700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-595100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-216300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-477600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1276400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-716900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-861400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>900200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-283700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1073400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>695200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>11500</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>566700</v>
+      </c>
+      <c r="E102" s="3">
         <v>332000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-453700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>323200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>302100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-344300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>696400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-910000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>259000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>496400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-153100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>500200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>255200</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -783,10 +783,10 @@
         <v>12731000</v>
       </c>
       <c r="F9" s="3">
-        <v>12865800</v>
+        <v>12728900</v>
       </c>
       <c r="G9" s="3">
-        <v>13275600</v>
+        <v>13142800</v>
       </c>
       <c r="H9" s="3">
         <v>13114900</v>
@@ -831,10 +831,10 @@
         <v>7609100</v>
       </c>
       <c r="F10" s="3">
-        <v>7521200</v>
+        <v>7658100</v>
       </c>
       <c r="G10" s="3">
-        <v>7626700</v>
+        <v>7759500</v>
       </c>
       <c r="H10" s="3">
         <v>9029700</v>
@@ -995,10 +995,10 @@
         <v>201000</v>
       </c>
       <c r="F14" s="3">
-        <v>-275000</v>
+        <v>-138100</v>
       </c>
       <c r="G14" s="3">
-        <v>-116200</v>
+        <v>16600</v>
       </c>
       <c r="H14" s="3">
         <v>321000</v>
@@ -1108,10 +1108,10 @@
         <v>19067900</v>
       </c>
       <c r="F17" s="3">
-        <v>19274900</v>
+        <v>19138000</v>
       </c>
       <c r="G17" s="3">
-        <v>19754500</v>
+        <v>19621700</v>
       </c>
       <c r="H17" s="3">
         <v>21122000</v>
@@ -1156,10 +1156,10 @@
         <v>1272200</v>
       </c>
       <c r="F18" s="3">
-        <v>1112100</v>
+        <v>1249000</v>
       </c>
       <c r="G18" s="3">
-        <v>1147800</v>
+        <v>1280600</v>
       </c>
       <c r="H18" s="3">
         <v>1022700</v>
@@ -1272,10 +1272,10 @@
         <v>4174800</v>
       </c>
       <c r="F21" s="3">
-        <v>4153400</v>
+        <v>4290300</v>
       </c>
       <c r="G21" s="3">
-        <v>4564900</v>
+        <v>4697700</v>
       </c>
       <c r="H21" s="3">
         <v>4602000</v>

--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>KT</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19566200</v>
+      </c>
+      <c r="E8" s="3">
         <v>17892200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20340100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20387000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20902300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22144700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21084700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21051900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22042300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17285200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16488100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18741800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21892700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20700800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19879000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>11697700</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3">
         <v>12731000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12728900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13142800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13114900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12689900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12354900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12434000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6724800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6518700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7504500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6253800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5936900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6602100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6194400</v>
+        <v>19566200</v>
       </c>
       <c r="E10" s="3">
+        <v>17892200</v>
+      </c>
+      <c r="F10" s="3">
         <v>7609100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7658100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7759500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9029700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8394800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8697000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9608300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10560400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9969400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11237300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15638900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14763900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13277000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>27000</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3">
         <v>48700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>74800</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>144200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>142900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>158800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>157900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>127600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>136000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>161300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>156000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>257300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>277000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>158700</v>
+        <v>143900</v>
       </c>
       <c r="E14" s="3">
+        <v>259800</v>
+      </c>
+      <c r="F14" s="3">
         <v>201000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-138100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>321000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>139200</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>40300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>115900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>89900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>39300</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2688000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2625000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2938200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2907000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3028700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3339500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3143800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2947900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3149500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2542400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2470600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2793600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3245200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2750200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2661700</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>17344200</v>
+        <v>17869400</v>
       </c>
       <c r="E17" s="3">
+        <v>17362100</v>
+      </c>
+      <c r="F17" s="3">
         <v>19067900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19138000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19621700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21122000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20080300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20063000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21041500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16231100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15647200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19173300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21603000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19292300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18090700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>548000</v>
+        <v>1696800</v>
       </c>
       <c r="E18" s="3">
+        <v>530000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1272200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1249000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1280600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1022700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1004400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>988900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1000800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1054100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>840900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-431500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>289700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1408400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1788400</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,104 +1244,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-8000</v>
+        <v>-146400</v>
       </c>
       <c r="E20" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="F20" s="3">
         <v>35700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-134300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-388400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-239800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>23300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>13500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>39900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>58800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-22900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-285500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>85400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>177300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>92500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3180900</v>
+        <v>4531200</v>
       </c>
       <c r="E21" s="3">
+        <v>3282000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4174800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4290300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4697700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4602000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4124900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3923300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4110400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3713200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3475200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2521100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3633700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4402500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4547700</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1317,143 +1356,152 @@
         <v>253600</v>
       </c>
       <c r="E22" s="3">
+        <v>253600</v>
+      </c>
+      <c r="F22" s="3">
         <v>274800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>233700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>221100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>242200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>241200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>266500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>283200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>256300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>285600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>399100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>409800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>397300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>432500</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1675100</v>
+      </c>
+      <c r="E23" s="3">
         <v>395800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1021100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1504000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1660900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>947900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>845600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>928800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>764800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>856500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>532400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1116000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-34700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1188500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1448300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>402700</v>
+      </c>
+      <c r="E24" s="3">
         <v>113500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>258600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>402200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>435700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>262200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>268800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>282600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>253400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>250200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>169600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-231800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>233400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>286600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1272400</v>
+      </c>
+      <c r="E26" s="3">
         <v>282300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>762500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1101800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1225200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>685700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>576800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>646200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>511400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>606400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>362800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-884200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-79800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>955100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1161700</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>317600</v>
+        <v>1199200</v>
       </c>
       <c r="E27" s="3">
+        <v>318400</v>
+      </c>
+      <c r="F27" s="3">
         <v>777900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1001600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1137200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>644000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>533400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>579900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>432100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>606400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>303900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-939900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-172800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>905200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1152000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1674,26 +1734,29 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-65900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>105300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>53700</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>148400</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>8000</v>
+        <v>146400</v>
       </c>
       <c r="E32" s="3">
+        <v>127000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-35700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>134300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>388400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>239800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-23300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-13500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-39900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-58800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>22900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>285500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-85400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-177300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-92500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1199200</v>
+      </c>
+      <c r="E33" s="3">
         <v>318400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>778800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1002300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1139100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>644000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>533400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>579900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>432100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>540400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>409200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-886200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-172800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>878700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1300400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1199200</v>
+      </c>
+      <c r="E35" s="3">
         <v>318400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>778800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1002300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1139100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>644000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>533400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>579900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>432100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>540400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>409200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-886200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-172800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>878700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1300400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2429500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2515900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2220600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1947400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2535000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2420900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1997300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2428400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1805000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2204200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1894000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1586500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1884500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2454100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>597300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1048500</v>
+      </c>
+      <c r="E42" s="3">
         <v>785600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1071000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1016800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>968900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1100200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>726000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>871000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>907900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>547600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>216800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>279500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>436900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1708200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1515700</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4162200</v>
+        <v>2035300</v>
       </c>
       <c r="E43" s="3">
+        <v>1977900</v>
+      </c>
+      <c r="F43" s="3">
         <v>5531900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4850200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4276000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4506700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5175100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5106100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5591900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4053300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3617500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4858500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5831100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7453300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5811000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>288300</v>
+      </c>
+      <c r="E44" s="3">
         <v>636500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>703500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>570700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>431600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>491300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>576400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>965300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>601000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>287300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>388800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>351900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>613000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1346800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>607300</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1547400</v>
+        <v>3878400</v>
       </c>
       <c r="E45" s="3">
+        <v>3731700</v>
+      </c>
+      <c r="F45" s="3">
         <v>1668700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1705500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1743700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1730400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1830400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1550100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>294700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>236500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>234500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>293700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>309000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>305200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>280300</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9680000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9647600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11195700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10090600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9955300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10249500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10305200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10921000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9200500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7328900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6351600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7370000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9074400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8834600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8811600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3273100</v>
+      </c>
+      <c r="E47" s="3">
         <v>2748100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3218700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3049500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1715100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1010900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>919000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>800200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>963900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1259900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1208000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2354300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2525800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3649000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3468200</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10943100</v>
+      </c>
+      <c r="E48" s="3">
         <v>10857100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12475000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12764300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13191500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14172300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13039200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11738800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12695700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11749700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11529900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14723400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15918100</v>
       </c>
-      <c r="P48" s="3" t="s">
+      <c r="Q48" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13663600</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>961800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1190500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1847100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2352100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2702400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1727800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2218600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2759500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2072700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2297300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1923800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2977000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3482900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5398000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2379100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4103600</v>
+      </c>
+      <c r="E52" s="3">
         <v>3216500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3393400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3425500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2586900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2330300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2127200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1889100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1663900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>610800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>699100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>966700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>712300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>593000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>554300</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29752700</v>
+      </c>
+      <c r="E54" s="3">
         <v>28349900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32935900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32593400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31195900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30932200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29918100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29170600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27985400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23246700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21712500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28391400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31713600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29028600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28876900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>792700</v>
+      </c>
+      <c r="E57" s="3">
         <v>701800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>914800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1290500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1139200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1130200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1110700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1309900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>939300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>954900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1008000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1562200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1531200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1471800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1994300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2879700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2596700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1704000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1747900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1620300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1367800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1548900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1472900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1383200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1322600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2499700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2766600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2697300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1942700</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5313200</v>
+      </c>
+      <c r="E59" s="3">
         <v>5810800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6541200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5888800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5417600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5687400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6292100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5778900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6086000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4871700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4116100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4881500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5885200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5235600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4456100</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8100200</v>
+      </c>
+      <c r="E60" s="3">
         <v>9392300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10138700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8507600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8456000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8446900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8790100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8438500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8868800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7194300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6393500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8389200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10213900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9464100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7870600</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6463300</v>
+      </c>
+      <c r="E61" s="3">
         <v>4959300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6211900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7211600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6324200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6153400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6021000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5078000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4783700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4788600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5182800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8311500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7745800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6944000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8078500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>755200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1005300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1337600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1291300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1637400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1162900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1184000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1699200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1416100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1539800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1133700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1789200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2071800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1517400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1643700</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16273100</v>
+      </c>
+      <c r="E66" s="3">
         <v>16167500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18622400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17952400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17287500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16642100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16766300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16003300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15644500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14550800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13687100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19707300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21041400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18688900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18343100</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10366600</v>
+      </c>
+      <c r="E72" s="3">
         <v>9328000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11177400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11335200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11155000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11169500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10077000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10111000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9324600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7339000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6703900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7197500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9117600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17885900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9197700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12231000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10973600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12916200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13207700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12573100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12875000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11835000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11794200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11038100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8695900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8025400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8684100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10672200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10339700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10533800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1199200</v>
+      </c>
+      <c r="E81" s="3">
         <v>318400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>778800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1002300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1139100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>644000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>533400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>579900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>432100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>540400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>409200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-886200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-172800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>878700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1300400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2306500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2218900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2449100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2451800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2554300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2792900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2599400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2457100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2623500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2600300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2693600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3238000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3294900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2783600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2696800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3423400</v>
+      </c>
+      <c r="E89" s="3">
         <v>3429200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4243900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2860200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4669300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4355400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3244000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3602500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3630000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3625800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3130200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1609800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3741100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4809400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1947600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1969500</v>
+        <v>-2491700</v>
       </c>
       <c r="E91" s="3">
+        <v>-1980700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2847800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2735200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2934100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2947400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2826600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2030900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2286200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2305600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2396400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2810200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3158600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3155000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3130100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1926200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3563100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3847500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4313000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3456400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3367300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2429000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3260700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2648600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1777400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2663600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3442200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3235000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2399100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>590500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>406300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>358100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>294100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>247900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>233600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>220200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>183500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-139900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-30800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-187100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-465300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-827100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1063400</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-437400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-941000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-349200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>532200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-34700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-595100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-216300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-477600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1276400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-716900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-861400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-283700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1073400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>695200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>11500</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-145300</v>
+      </c>
+      <c r="E102" s="3">
         <v>566700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>332000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-453700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>323200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>302100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-344300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>696400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-910000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>259000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>496400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-153100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>255200</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KT_YR_FIN.xlsx
@@ -1608,10 +1608,10 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1199200</v>
+        <v>1198400</v>
       </c>
       <c r="E27" s="3">
-        <v>318400</v>
+        <v>317600</v>
       </c>
       <c r="F27" s="3">
         <v>777900</v>
